--- a/research/traditional_assets/database/data/greece/greece_tobacco.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_tobacco.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08855779563816413</v>
+        <v>0.08839806848776018</v>
       </c>
       <c r="C2">
-        <v>961.82541186713</v>
+        <v>953.1241885937234</v>
       </c>
       <c r="D2">
-        <v>704.0254118671301</v>
+        <v>704.9419885937234</v>
       </c>
       <c r="E2">
-        <v>-1.68</v>
+        <v>7.937800000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.617800000000001</v>
       </c>
       <c r="G2">
         <v>257.8</v>
@@ -1451,28 +1451,28 @@
         <v>117.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.48377534</v>
       </c>
       <c r="N2">
-        <v>117.1</v>
+        <v>116.61622466</v>
       </c>
       <c r="O2">
-        <v>25.762</v>
+        <v>25.6555694252</v>
       </c>
       <c r="P2">
-        <v>91.33799999999999</v>
+        <v>90.9606552348</v>
       </c>
       <c r="Q2">
-        <v>98.438</v>
+        <v>98.06065523480001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08855779563816413</v>
+        <v>0.08889467524016179</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5616680847221195</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>242.0545040596737</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08839806848776018</v>
+        <v>0.0882383413373562</v>
       </c>
       <c r="C3">
-        <v>953.1241885937234</v>
+        <v>944.4253550297151</v>
       </c>
       <c r="D3">
-        <v>704.9419885937234</v>
+        <v>705.8609550297151</v>
       </c>
       <c r="E3">
-        <v>7.937800000000001</v>
+        <v>17.5556</v>
       </c>
       <c r="F3">
-        <v>9.617800000000001</v>
+        <v>19.2356</v>
       </c>
       <c r="G3">
         <v>257.8</v>
@@ -1533,28 +1533,28 @@
         <v>117.1</v>
       </c>
       <c r="M3">
-        <v>0.48377534</v>
+        <v>0.96755068</v>
       </c>
       <c r="N3">
-        <v>116.61622466</v>
+        <v>116.13244932</v>
       </c>
       <c r="O3">
-        <v>25.6555694252</v>
+        <v>25.5491388504</v>
       </c>
       <c r="P3">
-        <v>90.9606552348</v>
+        <v>90.58331046959999</v>
       </c>
       <c r="Q3">
-        <v>98.06065523480001</v>
+        <v>97.6833104696</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08889467524016179</v>
+        <v>0.08923842993607775</v>
       </c>
       <c r="T3">
-        <v>0.5616680847221195</v>
+        <v>0.5661483607792743</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>242.0545040596737</v>
+        <v>121.0272520298368</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0882383413373562</v>
+        <v>0.08807861418695223</v>
       </c>
       <c r="C4">
-        <v>944.4253550297151</v>
+        <v>935.7289205330212</v>
       </c>
       <c r="D4">
-        <v>705.8609550297151</v>
+        <v>706.7823205330211</v>
       </c>
       <c r="E4">
-        <v>17.5556</v>
+        <v>27.1734</v>
       </c>
       <c r="F4">
-        <v>19.2356</v>
+        <v>28.8534</v>
       </c>
       <c r="G4">
         <v>257.8</v>
@@ -1615,28 +1615,28 @@
         <v>117.1</v>
       </c>
       <c r="M4">
-        <v>0.96755068</v>
+        <v>1.45132602</v>
       </c>
       <c r="N4">
-        <v>116.13244932</v>
+        <v>115.64867398</v>
       </c>
       <c r="O4">
-        <v>25.5491388504</v>
+        <v>25.4427082756</v>
       </c>
       <c r="P4">
-        <v>90.58331046959999</v>
+        <v>90.2059657044</v>
       </c>
       <c r="Q4">
-        <v>97.6833104696</v>
+        <v>97.30596570440001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08923842993607775</v>
+        <v>0.08958927235768271</v>
       </c>
       <c r="T4">
-        <v>0.5661483607792743</v>
+        <v>0.57072101366235</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>121.0272520298368</v>
+        <v>80.68483468655789</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08807861418695223</v>
+        <v>0.08791888703654828</v>
       </c>
       <c r="C5">
-        <v>935.7289205330212</v>
+        <v>927.0348945104811</v>
       </c>
       <c r="D5">
-        <v>706.7823205330211</v>
+        <v>707.706094510481</v>
       </c>
       <c r="E5">
-        <v>27.1734</v>
+        <v>36.7912</v>
       </c>
       <c r="F5">
-        <v>28.8534</v>
+        <v>38.4712</v>
       </c>
       <c r="G5">
         <v>257.8</v>
@@ -1697,28 +1697,28 @@
         <v>117.1</v>
       </c>
       <c r="M5">
-        <v>1.45132602</v>
+        <v>1.93510136</v>
       </c>
       <c r="N5">
-        <v>115.64867398</v>
+        <v>115.16489864</v>
       </c>
       <c r="O5">
-        <v>25.4427082756</v>
+        <v>25.3362777008</v>
       </c>
       <c r="P5">
-        <v>90.2059657044</v>
+        <v>89.82862093919999</v>
       </c>
       <c r="Q5">
-        <v>97.30596570440001</v>
+        <v>96.9286209392</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08958927235768271</v>
+        <v>0.08994742399640446</v>
       </c>
       <c r="T5">
-        <v>0.57072101366235</v>
+        <v>0.5753889301471563</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>80.68483468655789</v>
+        <v>60.51362601491841</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08791888703654828</v>
+        <v>0.08775915988614431</v>
       </c>
       <c r="C6">
-        <v>927.0348945104811</v>
+        <v>918.343286418178</v>
       </c>
       <c r="D6">
-        <v>707.706094510481</v>
+        <v>708.632286418178</v>
       </c>
       <c r="E6">
-        <v>36.7912</v>
+        <v>46.409</v>
       </c>
       <c r="F6">
-        <v>38.4712</v>
+        <v>48.089</v>
       </c>
       <c r="G6">
         <v>257.8</v>
@@ -1779,28 +1779,28 @@
         <v>117.1</v>
       </c>
       <c r="M6">
-        <v>1.93510136</v>
+        <v>2.4188767</v>
       </c>
       <c r="N6">
-        <v>115.16489864</v>
+        <v>114.6811233</v>
       </c>
       <c r="O6">
-        <v>25.3362777008</v>
+        <v>25.229847126</v>
       </c>
       <c r="P6">
-        <v>89.82862093919999</v>
+        <v>89.451276174</v>
       </c>
       <c r="Q6">
-        <v>96.9286209392</v>
+        <v>96.55127617400001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08994742399640446</v>
+        <v>0.0903131156696256</v>
       </c>
       <c r="T6">
-        <v>0.5753889301471563</v>
+        <v>0.5801551185579585</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>60.51362601491841</v>
+        <v>48.41090081193473</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08775915988614431</v>
+        <v>0.08759943273574035</v>
       </c>
       <c r="C7">
-        <v>918.343286418178</v>
+        <v>909.6541057617618</v>
       </c>
       <c r="D7">
-        <v>708.632286418178</v>
+        <v>709.5609057617619</v>
       </c>
       <c r="E7">
-        <v>46.409</v>
+        <v>56.0268</v>
       </c>
       <c r="F7">
-        <v>48.089</v>
+        <v>57.7068</v>
       </c>
       <c r="G7">
         <v>257.8</v>
@@ -1861,28 +1861,28 @@
         <v>117.1</v>
       </c>
       <c r="M7">
-        <v>2.4188767</v>
+        <v>2.90265204</v>
       </c>
       <c r="N7">
-        <v>114.6811233</v>
+        <v>114.19734796</v>
       </c>
       <c r="O7">
-        <v>25.229847126</v>
+        <v>25.1234165512</v>
       </c>
       <c r="P7">
-        <v>89.451276174</v>
+        <v>89.07393140879999</v>
       </c>
       <c r="Q7">
-        <v>96.55127617400001</v>
+        <v>96.1739314088</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0903131156696256</v>
+        <v>0.09068658801674506</v>
       </c>
       <c r="T7">
-        <v>0.5801551185579585</v>
+        <v>0.5850227152328203</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>48.41090081193473</v>
+        <v>40.34241734327894</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08759943273574035</v>
+        <v>0.0874397055853364</v>
       </c>
       <c r="C8">
-        <v>909.6541057617618</v>
+        <v>900.9673620967743</v>
       </c>
       <c r="D8">
-        <v>709.5609057617619</v>
+        <v>710.4919620967743</v>
       </c>
       <c r="E8">
-        <v>56.02679999999999</v>
+        <v>65.64459999999998</v>
       </c>
       <c r="F8">
-        <v>57.70679999999999</v>
+        <v>67.32459999999999</v>
       </c>
       <c r="G8">
         <v>257.8</v>
@@ -1943,28 +1943,28 @@
         <v>117.1</v>
       </c>
       <c r="M8">
-        <v>2.90265204</v>
+        <v>3.386427379999999</v>
       </c>
       <c r="N8">
-        <v>114.19734796</v>
+        <v>113.71357262</v>
       </c>
       <c r="O8">
-        <v>25.1234165512</v>
+        <v>25.0169859764</v>
       </c>
       <c r="P8">
-        <v>89.07393140880001</v>
+        <v>88.6965866436</v>
       </c>
       <c r="Q8">
-        <v>96.17393140880002</v>
+        <v>95.79658664360001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09068658801674506</v>
+        <v>0.09106809202724343</v>
       </c>
       <c r="T8">
-        <v>0.5850227152328203</v>
+        <v>0.5899949914060663</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>40.34241734327895</v>
+        <v>34.57921486566767</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08743970558533641</v>
+        <v>0.08727997843493243</v>
       </c>
       <c r="C9">
-        <v>900.9673620967741</v>
+        <v>892.283065028976</v>
       </c>
       <c r="D9">
-        <v>710.4919620967742</v>
+        <v>711.4254650289761</v>
       </c>
       <c r="E9">
-        <v>65.6446</v>
+        <v>75.2624</v>
       </c>
       <c r="F9">
-        <v>67.3246</v>
+        <v>76.94240000000001</v>
       </c>
       <c r="G9">
         <v>257.8</v>
@@ -2025,28 +2025,28 @@
         <v>117.1</v>
       </c>
       <c r="M9">
-        <v>3.38642738</v>
+        <v>3.87020272</v>
       </c>
       <c r="N9">
-        <v>113.71357262</v>
+        <v>113.22979728</v>
       </c>
       <c r="O9">
-        <v>25.0169859764</v>
+        <v>24.9105554016</v>
       </c>
       <c r="P9">
-        <v>88.6965866436</v>
+        <v>88.31924187839999</v>
       </c>
       <c r="Q9">
-        <v>95.79658664360001</v>
+        <v>95.4192418784</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09106809202724345</v>
+        <v>0.09145788960318743</v>
       </c>
       <c r="T9">
-        <v>0.5899949914060664</v>
+        <v>0.5950753605396003</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>34.57921486566766</v>
+        <v>30.25681300745921</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08727997843493243</v>
+        <v>0.08712025128452849</v>
       </c>
       <c r="C10">
-        <v>892.283065028976</v>
+        <v>883.6012242146779</v>
       </c>
       <c r="D10">
-        <v>711.4254650289761</v>
+        <v>712.3614242146779</v>
       </c>
       <c r="E10">
-        <v>75.2624</v>
+        <v>84.88019999999999</v>
       </c>
       <c r="F10">
-        <v>76.94240000000001</v>
+        <v>86.56019999999999</v>
       </c>
       <c r="G10">
         <v>257.8</v>
@@ -2107,28 +2107,28 @@
         <v>117.1</v>
       </c>
       <c r="M10">
-        <v>3.87020272</v>
+        <v>4.353978059999999</v>
       </c>
       <c r="N10">
-        <v>113.22979728</v>
+        <v>112.74602194</v>
       </c>
       <c r="O10">
-        <v>24.9105554016</v>
+        <v>24.8041248268</v>
       </c>
       <c r="P10">
-        <v>88.31924187839999</v>
+        <v>87.94189711319999</v>
       </c>
       <c r="Q10">
-        <v>95.4192418784</v>
+        <v>95.04189711319999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09145788960318743</v>
+        <v>0.09185625415882251</v>
       </c>
       <c r="T10">
-        <v>0.5950753605396003</v>
+        <v>0.6002673861376076</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>30.25681300745921</v>
+        <v>26.89494489551929</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08712025128452849</v>
+        <v>0.08696052413412451</v>
       </c>
       <c r="C11">
-        <v>883.6012242146779</v>
+        <v>874.9218493610734</v>
       </c>
       <c r="D11">
-        <v>712.3614242146779</v>
+        <v>713.2998493610735</v>
       </c>
       <c r="E11">
-        <v>84.88019999999999</v>
+        <v>94.49799999999998</v>
       </c>
       <c r="F11">
-        <v>86.56019999999999</v>
+        <v>96.17799999999998</v>
       </c>
       <c r="G11">
         <v>257.8</v>
@@ -2189,28 +2189,28 @@
         <v>117.1</v>
       </c>
       <c r="M11">
-        <v>4.353978059999999</v>
+        <v>4.837753399999999</v>
       </c>
       <c r="N11">
-        <v>112.74602194</v>
+        <v>112.2622466</v>
       </c>
       <c r="O11">
-        <v>24.8041248268</v>
+        <v>24.697694252</v>
       </c>
       <c r="P11">
-        <v>87.94189711319999</v>
+        <v>87.56455234800001</v>
       </c>
       <c r="Q11">
-        <v>95.04189711319999</v>
+        <v>94.66455234800002</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09185625415882251</v>
+        <v>0.09226347126013835</v>
       </c>
       <c r="T11">
-        <v>0.6002673861376076</v>
+        <v>0.6055747900822371</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>26.89494489551929</v>
+        <v>24.20545040596737</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08696052413412451</v>
+        <v>0.08680079698372056</v>
       </c>
       <c r="C12">
-        <v>874.9218493610734</v>
+        <v>866.2449502265744</v>
       </c>
       <c r="D12">
-        <v>713.2998493610735</v>
+        <v>714.2407502265743</v>
       </c>
       <c r="E12">
-        <v>94.49799999999999</v>
+        <v>104.1158</v>
       </c>
       <c r="F12">
-        <v>96.178</v>
+        <v>105.7958</v>
       </c>
       <c r="G12">
         <v>257.8</v>
@@ -2271,28 +2271,28 @@
         <v>117.1</v>
       </c>
       <c r="M12">
-        <v>4.8377534</v>
+        <v>5.32152874</v>
       </c>
       <c r="N12">
-        <v>112.2622466</v>
+        <v>111.77847126</v>
       </c>
       <c r="O12">
-        <v>24.697694252</v>
+        <v>24.5912636772</v>
       </c>
       <c r="P12">
-        <v>87.56455234800001</v>
+        <v>87.1872075828</v>
       </c>
       <c r="Q12">
-        <v>94.66455234800002</v>
+        <v>94.28720758280001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09226347126013835</v>
+        <v>0.09267983930755119</v>
       </c>
       <c r="T12">
-        <v>0.6055747900822371</v>
+        <v>0.6110014615312405</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>24.20545040596737</v>
+        <v>22.00495491451579</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08680079698372056</v>
+        <v>0.08664106983331661</v>
       </c>
       <c r="C13">
-        <v>866.2449502265744</v>
+        <v>857.5705366211488</v>
       </c>
       <c r="D13">
-        <v>714.2407502265743</v>
+        <v>715.1841366211488</v>
       </c>
       <c r="E13">
-        <v>104.1158</v>
+        <v>113.7336</v>
       </c>
       <c r="F13">
-        <v>105.7958</v>
+        <v>115.4136</v>
       </c>
       <c r="G13">
         <v>257.8</v>
@@ -2353,28 +2353,28 @@
         <v>117.1</v>
       </c>
       <c r="M13">
-        <v>5.32152874</v>
+        <v>5.805304079999999</v>
       </c>
       <c r="N13">
-        <v>111.77847126</v>
+        <v>111.29469592</v>
       </c>
       <c r="O13">
-        <v>24.5912636772</v>
+        <v>24.4848331024</v>
       </c>
       <c r="P13">
-        <v>87.1872075828</v>
+        <v>86.80986281759999</v>
       </c>
       <c r="Q13">
-        <v>94.28720758280001</v>
+        <v>93.9098628176</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09267983930755119</v>
+        <v>0.0931056702651325</v>
       </c>
       <c r="T13">
-        <v>0.6110014615312405</v>
+        <v>0.6165514664222665</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>22.00495491451579</v>
+        <v>20.17120867163947</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08664106983331661</v>
+        <v>0.08648134268291262</v>
       </c>
       <c r="C14">
-        <v>857.5705366211488</v>
+        <v>848.8986184066631</v>
       </c>
       <c r="D14">
-        <v>715.1841366211488</v>
+        <v>716.1300184066631</v>
       </c>
       <c r="E14">
-        <v>113.7336</v>
+        <v>123.3514</v>
       </c>
       <c r="F14">
-        <v>115.4136</v>
+        <v>125.0314</v>
       </c>
       <c r="G14">
         <v>257.8</v>
@@ -2435,28 +2435,28 @@
         <v>117.1</v>
       </c>
       <c r="M14">
-        <v>5.805304079999999</v>
+        <v>6.28907942</v>
       </c>
       <c r="N14">
-        <v>111.29469592</v>
+        <v>110.81092058</v>
       </c>
       <c r="O14">
-        <v>24.4848331024</v>
+        <v>24.3784025276</v>
       </c>
       <c r="P14">
-        <v>86.80986281759999</v>
+        <v>86.43251805239998</v>
       </c>
       <c r="Q14">
-        <v>93.9098628176</v>
+        <v>93.53251805239999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0931056702651325</v>
+        <v>0.09354129044012946</v>
       </c>
       <c r="T14">
-        <v>0.6165514664222665</v>
+        <v>0.6222290576326265</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>20.17120867163947</v>
+        <v>18.61957723535951</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08648134268291262</v>
+        <v>0.08632161553250867</v>
       </c>
       <c r="C15">
-        <v>848.8986184066631</v>
+        <v>840.2292054972236</v>
       </c>
       <c r="D15">
-        <v>716.1300184066631</v>
+        <v>717.0784054972237</v>
       </c>
       <c r="E15">
-        <v>123.3514</v>
+        <v>132.9692</v>
       </c>
       <c r="F15">
-        <v>125.0314</v>
+        <v>134.6492</v>
       </c>
       <c r="G15">
         <v>257.8</v>
@@ -2517,28 +2517,28 @@
         <v>117.1</v>
       </c>
       <c r="M15">
-        <v>6.28907942</v>
+        <v>6.77285476</v>
       </c>
       <c r="N15">
-        <v>110.81092058</v>
+        <v>110.32714524</v>
       </c>
       <c r="O15">
-        <v>24.3784025276</v>
+        <v>24.2719719528</v>
       </c>
       <c r="P15">
-        <v>86.43251805239998</v>
+        <v>86.05517328719999</v>
       </c>
       <c r="Q15">
-        <v>93.53251805239999</v>
+        <v>93.1551732872</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09354129044012946</v>
+        <v>0.09398704131687055</v>
       </c>
       <c r="T15">
-        <v>0.6222290576326265</v>
+        <v>0.6280386858478787</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>18.61957723535951</v>
+        <v>17.28960743283383</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08632161553250867</v>
+        <v>0.08616188838210471</v>
       </c>
       <c r="C16">
-        <v>840.2292054972236</v>
+        <v>831.5623078595256</v>
       </c>
       <c r="D16">
-        <v>717.0784054972237</v>
+        <v>718.0293078595257</v>
       </c>
       <c r="E16">
-        <v>132.9692</v>
+        <v>142.587</v>
       </c>
       <c r="F16">
-        <v>134.6492</v>
+        <v>144.267</v>
       </c>
       <c r="G16">
         <v>257.8</v>
@@ -2599,28 +2599,28 @@
         <v>117.1</v>
       </c>
       <c r="M16">
-        <v>6.77285476</v>
+        <v>7.256630100000001</v>
       </c>
       <c r="N16">
-        <v>110.32714524</v>
+        <v>109.8433699</v>
       </c>
       <c r="O16">
-        <v>24.2719719528</v>
+        <v>24.165541378</v>
       </c>
       <c r="P16">
-        <v>86.05517328719999</v>
+        <v>85.677828522</v>
       </c>
       <c r="Q16">
-        <v>93.1551732872</v>
+        <v>92.77782852200001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09398704131687055</v>
+        <v>0.09444328044953496</v>
       </c>
       <c r="T16">
-        <v>0.6280386858478787</v>
+        <v>0.6339850111976073</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>17.28960743283383</v>
+        <v>16.13696693731158</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08616188838210471</v>
+        <v>0.08600216123170075</v>
       </c>
       <c r="C17">
-        <v>831.5623078595256</v>
+        <v>822.8979355132001</v>
       </c>
       <c r="D17">
-        <v>718.0293078595257</v>
+        <v>718.9827355132001</v>
       </c>
       <c r="E17">
-        <v>142.587</v>
+        <v>152.2048</v>
       </c>
       <c r="F17">
-        <v>144.267</v>
+        <v>153.8848</v>
       </c>
       <c r="G17">
         <v>257.8</v>
@@ -2681,28 +2681,28 @@
         <v>117.1</v>
       </c>
       <c r="M17">
-        <v>7.2566301</v>
+        <v>7.74040544</v>
       </c>
       <c r="N17">
-        <v>109.8433699</v>
+        <v>109.35959456</v>
       </c>
       <c r="O17">
-        <v>24.165541378</v>
+        <v>24.0591108032</v>
       </c>
       <c r="P17">
-        <v>85.677828522</v>
+        <v>85.30048375679999</v>
       </c>
       <c r="Q17">
-        <v>92.77782852200001</v>
+        <v>92.4004837568</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09444328044953496</v>
+        <v>0.09491038241869137</v>
       </c>
       <c r="T17">
-        <v>0.6339850111976073</v>
+        <v>0.6400729157223295</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.13696693731158</v>
+        <v>15.1284065037296</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08600216123170075</v>
+        <v>0.08584243408129678</v>
       </c>
       <c r="C18">
-        <v>822.8979355132001</v>
+        <v>814.236098531167</v>
       </c>
       <c r="D18">
-        <v>718.9827355132001</v>
+        <v>719.938698531167</v>
       </c>
       <c r="E18">
-        <v>152.2048</v>
+        <v>161.8226</v>
       </c>
       <c r="F18">
-        <v>153.8848</v>
+        <v>163.5026</v>
       </c>
       <c r="G18">
         <v>257.8</v>
@@ -2763,28 +2763,28 @@
         <v>117.1</v>
       </c>
       <c r="M18">
-        <v>7.74040544</v>
+        <v>8.224180779999999</v>
       </c>
       <c r="N18">
-        <v>109.35959456</v>
+        <v>108.87581922</v>
       </c>
       <c r="O18">
-        <v>24.0591108032</v>
+        <v>23.9526802284</v>
       </c>
       <c r="P18">
-        <v>85.30048375679999</v>
+        <v>84.9231389916</v>
       </c>
       <c r="Q18">
-        <v>92.4004837568</v>
+        <v>92.02313899160001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09491038241869137</v>
+        <v>0.09538873985698408</v>
       </c>
       <c r="T18">
-        <v>0.6400729157223295</v>
+        <v>0.6463075167416233</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.1284065037296</v>
+        <v>14.23850023880433</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08584243408129678</v>
+        <v>0.08568270693089282</v>
       </c>
       <c r="C19">
-        <v>814.236098531167</v>
+        <v>805.5768070399893</v>
       </c>
       <c r="D19">
-        <v>719.938698531167</v>
+        <v>720.8972070399893</v>
       </c>
       <c r="E19">
-        <v>161.8226</v>
+        <v>171.4404</v>
       </c>
       <c r="F19">
-        <v>163.5026</v>
+        <v>173.1204</v>
       </c>
       <c r="G19">
         <v>257.8</v>
@@ -2845,28 +2845,28 @@
         <v>117.1</v>
       </c>
       <c r="M19">
-        <v>8.224180779999999</v>
+        <v>8.70795612</v>
       </c>
       <c r="N19">
-        <v>108.87581922</v>
+        <v>108.39204388</v>
       </c>
       <c r="O19">
-        <v>23.9526802284</v>
+        <v>23.8462496536</v>
       </c>
       <c r="P19">
-        <v>84.9231389916</v>
+        <v>84.54579422639999</v>
       </c>
       <c r="Q19">
-        <v>92.02313899160001</v>
+        <v>91.6457942264</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09538873985698408</v>
+        <v>0.09587876454986929</v>
       </c>
       <c r="T19">
-        <v>0.6463075167416233</v>
+        <v>0.6526941812004121</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.23850023880433</v>
+        <v>13.44747244775965</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08568270693089283</v>
+        <v>0.08574527978048888</v>
       </c>
       <c r="C20">
-        <v>805.5768070399893</v>
+        <v>795.5832089805267</v>
       </c>
       <c r="D20">
-        <v>720.8972070399892</v>
+        <v>720.5214089805268</v>
       </c>
       <c r="E20">
-        <v>171.4404</v>
+        <v>181.0582</v>
       </c>
       <c r="F20">
-        <v>173.1204</v>
+        <v>182.7382</v>
       </c>
       <c r="G20">
         <v>257.8</v>
@@ -2927,45 +2927,45 @@
         <v>117.1</v>
       </c>
       <c r="M20">
-        <v>8.707956119999999</v>
+        <v>9.46583876</v>
       </c>
       <c r="N20">
-        <v>108.39204388</v>
+        <v>107.63416124</v>
       </c>
       <c r="O20">
-        <v>23.8462496536</v>
+        <v>23.6795154728</v>
       </c>
       <c r="P20">
-        <v>84.54579422639999</v>
+        <v>83.95464576719999</v>
       </c>
       <c r="Q20">
-        <v>91.6457942264</v>
+        <v>91.0546457672</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09587876454986929</v>
+        <v>0.09638088861788749</v>
       </c>
       <c r="T20">
-        <v>0.652694181200412</v>
+        <v>0.6592385410779363</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>13.44747244775965</v>
+        <v>12.37080019731923</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08574527978048888</v>
+        <v>0.08559725263008491</v>
       </c>
       <c r="C21">
-        <v>795.5832089805267</v>
+        <v>786.8550594895714</v>
       </c>
       <c r="D21">
-        <v>720.5214089805268</v>
+        <v>721.4110594895715</v>
       </c>
       <c r="E21">
-        <v>181.0582</v>
+        <v>190.676</v>
       </c>
       <c r="F21">
-        <v>182.7382</v>
+        <v>192.356</v>
       </c>
       <c r="G21">
         <v>257.8</v>
@@ -3009,28 +3009,28 @@
         <v>117.1</v>
       </c>
       <c r="M21">
-        <v>9.46583876</v>
+        <v>9.964040799999999</v>
       </c>
       <c r="N21">
-        <v>107.63416124</v>
+        <v>107.1359592</v>
       </c>
       <c r="O21">
-        <v>23.6795154728</v>
+        <v>23.569911024</v>
       </c>
       <c r="P21">
-        <v>83.95464576719999</v>
+        <v>83.56604817600001</v>
       </c>
       <c r="Q21">
-        <v>91.0546457672</v>
+        <v>90.66604817600002</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09638088861788749</v>
+        <v>0.09689556578760614</v>
       </c>
       <c r="T21">
-        <v>0.6592385410779363</v>
+        <v>0.6659465099523988</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>12.37080019731923</v>
+        <v>11.75226018745327</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08559725263008491</v>
+        <v>0.08544922547968095</v>
       </c>
       <c r="C22">
-        <v>786.8550594895714</v>
+        <v>778.1291096737109</v>
       </c>
       <c r="D22">
-        <v>721.4110594895715</v>
+        <v>722.3029096737108</v>
       </c>
       <c r="E22">
-        <v>190.676</v>
+        <v>200.2938</v>
       </c>
       <c r="F22">
-        <v>192.356</v>
+        <v>201.9738</v>
       </c>
       <c r="G22">
         <v>257.8</v>
@@ -3091,28 +3091,28 @@
         <v>117.1</v>
       </c>
       <c r="M22">
-        <v>9.964040799999999</v>
+        <v>10.46224284</v>
       </c>
       <c r="N22">
-        <v>107.1359592</v>
+        <v>106.63775716</v>
       </c>
       <c r="O22">
-        <v>23.569911024</v>
+        <v>23.4603065752</v>
       </c>
       <c r="P22">
-        <v>83.56604817600001</v>
+        <v>83.1774505848</v>
       </c>
       <c r="Q22">
-        <v>90.66604817600002</v>
+        <v>90.27745058480001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09689556578760614</v>
+        <v>0.0974232727590898</v>
       </c>
       <c r="T22">
-        <v>0.6659465099523988</v>
+        <v>0.6728243008236831</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.75226018745327</v>
+        <v>11.19262874995549</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08544922547968095</v>
+        <v>0.08530119832927698</v>
       </c>
       <c r="C23">
-        <v>778.1291096737109</v>
+        <v>769.4053677011409</v>
       </c>
       <c r="D23">
-        <v>722.3029096737108</v>
+        <v>723.1969677011409</v>
       </c>
       <c r="E23">
-        <v>200.2938</v>
+        <v>209.9116</v>
       </c>
       <c r="F23">
-        <v>201.9738</v>
+        <v>211.5916</v>
       </c>
       <c r="G23">
         <v>257.8</v>
@@ -3173,28 +3173,28 @@
         <v>117.1</v>
       </c>
       <c r="M23">
-        <v>10.46224284</v>
+        <v>10.96044488</v>
       </c>
       <c r="N23">
-        <v>106.63775716</v>
+        <v>106.13955512</v>
       </c>
       <c r="O23">
-        <v>23.4603065752</v>
+        <v>23.3507021264</v>
       </c>
       <c r="P23">
-        <v>83.1774505848</v>
+        <v>82.7888529936</v>
       </c>
       <c r="Q23">
-        <v>90.27745058480001</v>
+        <v>89.88885299360001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0974232727590898</v>
+        <v>0.09796451067856023</v>
       </c>
       <c r="T23">
-        <v>0.6728243008236829</v>
+        <v>0.6798784453070514</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.19262874995549</v>
+        <v>10.68387289768479</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08530119832927698</v>
+        <v>0.08515317117887303</v>
       </c>
       <c r="C24">
-        <v>769.4053677011409</v>
+        <v>760.6838417805491</v>
       </c>
       <c r="D24">
-        <v>723.1969677011409</v>
+        <v>724.093241780549</v>
       </c>
       <c r="E24">
-        <v>209.9116</v>
+        <v>219.5294</v>
       </c>
       <c r="F24">
-        <v>211.5916</v>
+        <v>221.2094</v>
       </c>
       <c r="G24">
         <v>257.8</v>
@@ -3255,28 +3255,28 @@
         <v>117.1</v>
       </c>
       <c r="M24">
-        <v>10.96044488</v>
+        <v>11.45864692</v>
       </c>
       <c r="N24">
-        <v>106.13955512</v>
+        <v>105.64135308</v>
       </c>
       <c r="O24">
-        <v>23.3507021264</v>
+        <v>23.2410976776</v>
       </c>
       <c r="P24">
-        <v>82.7888529936</v>
+        <v>82.40025540239999</v>
       </c>
       <c r="Q24">
-        <v>89.88885299360001</v>
+        <v>89.5002554024</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09796451067856023</v>
+        <v>0.09851980672580912</v>
       </c>
       <c r="T24">
-        <v>0.6798784453070514</v>
+        <v>0.6871158143224555</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.68387289768479</v>
+        <v>10.21935668474197</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08515317117887303</v>
+        <v>0.08532338402846908</v>
       </c>
       <c r="C25">
-        <v>760.6838417805491</v>
+        <v>750.0356289928247</v>
       </c>
       <c r="D25">
-        <v>724.093241780549</v>
+        <v>723.0628289928246</v>
       </c>
       <c r="E25">
-        <v>219.5294</v>
+        <v>229.1472</v>
       </c>
       <c r="F25">
-        <v>221.2094</v>
+        <v>230.8272</v>
       </c>
       <c r="G25">
         <v>257.8</v>
@@ -3337,45 +3337,45 @@
         <v>117.1</v>
       </c>
       <c r="M25">
-        <v>11.45864692</v>
+        <v>12.3492552</v>
       </c>
       <c r="N25">
-        <v>105.64135308</v>
+        <v>104.7507448</v>
       </c>
       <c r="O25">
-        <v>23.2410976776</v>
+        <v>23.045163856</v>
       </c>
       <c r="P25">
-        <v>82.40025540239999</v>
+        <v>81.70558094399999</v>
       </c>
       <c r="Q25">
-        <v>89.5002554024</v>
+        <v>88.805580944</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09851980672580912</v>
+        <v>0.09908971582693299</v>
       </c>
       <c r="T25">
-        <v>0.6871158143224555</v>
+        <v>0.6945436404172123</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>10.21935668474197</v>
+        <v>9.482353235359488</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08532338402846908</v>
+        <v>0.0851886168780651</v>
       </c>
       <c r="C26">
-        <v>750.0356289928247</v>
+        <v>741.2334231021066</v>
       </c>
       <c r="D26">
-        <v>723.0628289928246</v>
+        <v>723.8784231021065</v>
       </c>
       <c r="E26">
-        <v>229.1472</v>
+        <v>238.765</v>
       </c>
       <c r="F26">
-        <v>230.8272</v>
+        <v>240.445</v>
       </c>
       <c r="G26">
         <v>257.8</v>
@@ -3419,28 +3419,28 @@
         <v>117.1</v>
       </c>
       <c r="M26">
-        <v>12.3492552</v>
+        <v>12.8638075</v>
       </c>
       <c r="N26">
-        <v>104.7507448</v>
+        <v>104.2361925</v>
       </c>
       <c r="O26">
-        <v>23.045163856</v>
+        <v>22.93196235</v>
       </c>
       <c r="P26">
-        <v>81.70558094399999</v>
+        <v>81.30423015</v>
       </c>
       <c r="Q26">
-        <v>88.805580944</v>
+        <v>88.40423015</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09908971582693299</v>
+        <v>0.0996748225040868</v>
       </c>
       <c r="T26">
-        <v>0.6945436404172123</v>
+        <v>0.7021695418744958</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.48235323535949</v>
+        <v>9.103059105945109</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0851886168780651</v>
+        <v>0.08505384972766115</v>
       </c>
       <c r="C27">
-        <v>741.2334231021066</v>
+        <v>732.4330592225971</v>
       </c>
       <c r="D27">
-        <v>723.8784231021065</v>
+        <v>724.6958592225971</v>
       </c>
       <c r="E27">
-        <v>238.765</v>
+        <v>248.3828</v>
       </c>
       <c r="F27">
-        <v>240.445</v>
+        <v>250.0628</v>
       </c>
       <c r="G27">
         <v>257.8</v>
@@ -3501,28 +3501,28 @@
         <v>117.1</v>
       </c>
       <c r="M27">
-        <v>12.8638075</v>
+        <v>13.3783598</v>
       </c>
       <c r="N27">
-        <v>104.2361925</v>
+        <v>103.7216402</v>
       </c>
       <c r="O27">
-        <v>22.93196235</v>
+        <v>22.818760844</v>
       </c>
       <c r="P27">
-        <v>81.30423015</v>
+        <v>80.902879356</v>
       </c>
       <c r="Q27">
-        <v>88.40423015</v>
+        <v>88.00287935600001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0996748225040868</v>
+        <v>0.1002757428752178</v>
       </c>
       <c r="T27">
-        <v>0.7021695418744958</v>
+        <v>0.7100015487765708</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>9.103059105945109</v>
+        <v>8.752941448024144</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08505384972766115</v>
+        <v>0.08491908257725718</v>
       </c>
       <c r="C28">
-        <v>732.4330592225971</v>
+        <v>723.6345436015973</v>
       </c>
       <c r="D28">
-        <v>724.6958592225971</v>
+        <v>725.5151436015974</v>
       </c>
       <c r="E28">
-        <v>248.3828</v>
+        <v>258.0006</v>
       </c>
       <c r="F28">
-        <v>250.0628</v>
+        <v>259.6806</v>
       </c>
       <c r="G28">
         <v>257.8</v>
@@ -3583,28 +3583,28 @@
         <v>117.1</v>
       </c>
       <c r="M28">
-        <v>13.3783598</v>
+        <v>13.8929121</v>
       </c>
       <c r="N28">
-        <v>103.7216402</v>
+        <v>103.2070879</v>
       </c>
       <c r="O28">
-        <v>22.818760844</v>
+        <v>22.705559338</v>
       </c>
       <c r="P28">
-        <v>80.902879356</v>
+        <v>80.50152856199999</v>
       </c>
       <c r="Q28">
-        <v>88.00287935600001</v>
+        <v>87.601528562</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1002757428752178</v>
+        <v>0.1008931268181605</v>
       </c>
       <c r="T28">
-        <v>0.7100015487765708</v>
+        <v>0.7180481312102096</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.752941448024144</v>
+        <v>8.428758431430655</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08491908257725718</v>
+        <v>0.08478431542685322</v>
       </c>
       <c r="C29">
-        <v>723.6345436015973</v>
+        <v>714.8378825146909</v>
       </c>
       <c r="D29">
-        <v>725.5151436015974</v>
+        <v>726.3362825146909</v>
       </c>
       <c r="E29">
-        <v>258.0006</v>
+        <v>267.6184</v>
       </c>
       <c r="F29">
-        <v>259.6806</v>
+        <v>269.2984</v>
       </c>
       <c r="G29">
         <v>257.8</v>
@@ -3665,28 +3665,28 @@
         <v>117.1</v>
       </c>
       <c r="M29">
-        <v>13.8929121</v>
+        <v>14.4074644</v>
       </c>
       <c r="N29">
-        <v>103.2070879</v>
+        <v>102.6925356</v>
       </c>
       <c r="O29">
-        <v>22.705559338</v>
+        <v>22.592357832</v>
       </c>
       <c r="P29">
-        <v>80.50152856199999</v>
+        <v>80.10017776799999</v>
       </c>
       <c r="Q29">
-        <v>87.601528562</v>
+        <v>87.200177768</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1008931268181605</v>
+        <v>0.1015276603150739</v>
       </c>
       <c r="T29">
-        <v>0.7180481312102096</v>
+        <v>0.7263182298225606</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.428758431430655</v>
+        <v>8.127731344593847</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08478431542685322</v>
+        <v>0.08464954827644926</v>
       </c>
       <c r="C30">
-        <v>714.8378825146909</v>
+        <v>706.0430822659042</v>
       </c>
       <c r="D30">
-        <v>726.3362825146909</v>
+        <v>727.1592822659043</v>
       </c>
       <c r="E30">
-        <v>267.6184</v>
+        <v>277.2362</v>
       </c>
       <c r="F30">
-        <v>269.2984</v>
+        <v>278.9162</v>
       </c>
       <c r="G30">
         <v>257.8</v>
@@ -3747,28 +3747,28 @@
         <v>117.1</v>
       </c>
       <c r="M30">
-        <v>14.4074644</v>
+        <v>14.9220167</v>
       </c>
       <c r="N30">
-        <v>102.6925356</v>
+        <v>102.1779833</v>
       </c>
       <c r="O30">
-        <v>22.592357832</v>
+        <v>22.479156326</v>
       </c>
       <c r="P30">
-        <v>80.10017776799999</v>
+        <v>79.698826974</v>
       </c>
       <c r="Q30">
-        <v>87.200177768</v>
+        <v>86.79882697400001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1015276603150739</v>
+        <v>0.102180067994999</v>
       </c>
       <c r="T30">
-        <v>0.7263182298225606</v>
+        <v>0.734821288959203</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.127731344593847</v>
+        <v>7.847464746504405</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08464954827644924</v>
+        <v>0.08470198112604529</v>
       </c>
       <c r="C31">
-        <v>706.0430822659043</v>
+        <v>696.1048623363105</v>
       </c>
       <c r="D31">
-        <v>727.1592822659043</v>
+        <v>726.8388623363105</v>
       </c>
       <c r="E31">
-        <v>277.2361999999999</v>
+        <v>286.854</v>
       </c>
       <c r="F31">
-        <v>278.9161999999999</v>
+        <v>288.534</v>
       </c>
       <c r="G31">
         <v>257.8</v>
@@ -3829,45 +3829,45 @@
         <v>117.1</v>
       </c>
       <c r="M31">
-        <v>14.9220167</v>
+        <v>15.6673962</v>
       </c>
       <c r="N31">
-        <v>102.1779833</v>
+        <v>101.4326038</v>
       </c>
       <c r="O31">
-        <v>22.479156326</v>
+        <v>22.315172836</v>
       </c>
       <c r="P31">
-        <v>79.698826974</v>
+        <v>79.11743096399999</v>
       </c>
       <c r="Q31">
-        <v>86.79882697400001</v>
+        <v>86.217430964</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.102180067994999</v>
+        <v>0.1028511158943504</v>
       </c>
       <c r="T31">
-        <v>0.734821288959203</v>
+        <v>0.7435672926426067</v>
       </c>
       <c r="U31">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y31">
-        <v>7.847464746504406</v>
+        <v>7.474120045550389</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08470198112604529</v>
+        <v>0.08457345397564132</v>
       </c>
       <c r="C32">
-        <v>696.1048623363105</v>
+        <v>687.2730014083608</v>
       </c>
       <c r="D32">
-        <v>726.8388623363105</v>
+        <v>727.6248014083607</v>
       </c>
       <c r="E32">
-        <v>286.854</v>
+        <v>296.4718</v>
       </c>
       <c r="F32">
-        <v>288.534</v>
+        <v>298.1518</v>
       </c>
       <c r="G32">
         <v>257.8</v>
@@ -3911,28 +3911,28 @@
         <v>117.1</v>
       </c>
       <c r="M32">
-        <v>15.6673962</v>
+        <v>16.18964274</v>
       </c>
       <c r="N32">
-        <v>101.4326038</v>
+        <v>100.91035726</v>
       </c>
       <c r="O32">
-        <v>22.315172836</v>
+        <v>22.2002785972</v>
       </c>
       <c r="P32">
-        <v>79.11743096399999</v>
+        <v>78.7100786628</v>
       </c>
       <c r="Q32">
-        <v>86.217430964</v>
+        <v>85.81007866280001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1028511158943504</v>
+        <v>0.1035416144574512</v>
       </c>
       <c r="T32">
-        <v>0.7435672926426067</v>
+        <v>0.7525668036791525</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.474120045550389</v>
+        <v>7.233019398919732</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08457345397564132</v>
+        <v>0.08444492682523737</v>
       </c>
       <c r="C33">
-        <v>687.2730014083608</v>
+        <v>678.4428420098866</v>
       </c>
       <c r="D33">
-        <v>727.6248014083607</v>
+        <v>728.4124420098867</v>
       </c>
       <c r="E33">
-        <v>296.4718</v>
+        <v>306.0896</v>
       </c>
       <c r="F33">
-        <v>298.1518</v>
+        <v>307.7696</v>
       </c>
       <c r="G33">
         <v>257.8</v>
@@ -3993,28 +3993,28 @@
         <v>117.1</v>
       </c>
       <c r="M33">
-        <v>16.18964274</v>
+        <v>16.71188928</v>
       </c>
       <c r="N33">
-        <v>100.91035726</v>
+        <v>100.38811072</v>
       </c>
       <c r="O33">
-        <v>22.2002785972</v>
+        <v>22.0853843584</v>
       </c>
       <c r="P33">
-        <v>78.7100786628</v>
+        <v>78.30272636159999</v>
       </c>
       <c r="Q33">
-        <v>85.81007866280001</v>
+        <v>85.4027263616</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1035416144574512</v>
+        <v>0.1042524218018197</v>
       </c>
       <c r="T33">
-        <v>0.7525668036791525</v>
+        <v>0.7618310062167732</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.233019398919732</v>
+        <v>7.006987542703489</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08444492682523737</v>
+        <v>0.0843163996748334</v>
       </c>
       <c r="C34">
-        <v>678.4428420098866</v>
+        <v>669.6143896725005</v>
       </c>
       <c r="D34">
-        <v>728.4124420098867</v>
+        <v>729.2017896725005</v>
       </c>
       <c r="E34">
-        <v>306.0896</v>
+        <v>315.7074</v>
       </c>
       <c r="F34">
-        <v>307.7696</v>
+        <v>317.3874</v>
       </c>
       <c r="G34">
         <v>257.8</v>
@@ -4075,28 +4075,28 @@
         <v>117.1</v>
       </c>
       <c r="M34">
-        <v>16.71188928</v>
+        <v>17.23413582</v>
       </c>
       <c r="N34">
-        <v>100.38811072</v>
+        <v>99.86586417999999</v>
       </c>
       <c r="O34">
-        <v>22.0853843584</v>
+        <v>21.9704901196</v>
       </c>
       <c r="P34">
-        <v>78.30272636159999</v>
+        <v>77.89537406039999</v>
       </c>
       <c r="Q34">
-        <v>85.4027263616</v>
+        <v>84.9953740604</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1042524218018197</v>
+        <v>0.1049844472758708</v>
       </c>
       <c r="T34">
-        <v>0.7618310062167732</v>
+        <v>0.7713717521137259</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.006987542703489</v>
+        <v>6.794654586863989</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0843163996748334</v>
+        <v>0.08418787252442944</v>
       </c>
       <c r="C35">
-        <v>669.6143896725005</v>
+        <v>660.7876499518172</v>
       </c>
       <c r="D35">
-        <v>729.2017896725005</v>
+        <v>729.9928499518172</v>
       </c>
       <c r="E35">
-        <v>315.7074</v>
+        <v>325.3252</v>
       </c>
       <c r="F35">
-        <v>317.3874</v>
+        <v>327.0052</v>
       </c>
       <c r="G35">
         <v>257.8</v>
@@ -4157,28 +4157,28 @@
         <v>117.1</v>
       </c>
       <c r="M35">
-        <v>17.23413582</v>
+        <v>17.75638236</v>
       </c>
       <c r="N35">
-        <v>99.86586417999999</v>
+        <v>99.34361763999999</v>
       </c>
       <c r="O35">
-        <v>21.9704901196</v>
+        <v>21.8555958808</v>
       </c>
       <c r="P35">
-        <v>77.89537406039999</v>
+        <v>77.4880217592</v>
       </c>
       <c r="Q35">
-        <v>84.9953740604</v>
+        <v>84.5880217592</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1049844472758708</v>
+        <v>0.1057386553400446</v>
       </c>
       <c r="T35">
-        <v>0.7713717521137259</v>
+        <v>0.7812016115227075</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.794654586863989</v>
+        <v>6.594811804897402</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08418787252442944</v>
+        <v>0.08405934537402548</v>
       </c>
       <c r="C36">
-        <v>660.7876499518172</v>
+        <v>651.9626284275862</v>
       </c>
       <c r="D36">
-        <v>729.9928499518172</v>
+        <v>730.7856284275863</v>
       </c>
       <c r="E36">
-        <v>325.3252</v>
+        <v>334.943</v>
       </c>
       <c r="F36">
-        <v>327.0052</v>
+        <v>336.623</v>
       </c>
       <c r="G36">
         <v>257.8</v>
@@ -4239,28 +4239,28 @@
         <v>117.1</v>
       </c>
       <c r="M36">
-        <v>17.75638236</v>
+        <v>18.2786289</v>
       </c>
       <c r="N36">
-        <v>99.34361763999999</v>
+        <v>98.82137109999999</v>
       </c>
       <c r="O36">
-        <v>21.8555958808</v>
+        <v>21.740701642</v>
       </c>
       <c r="P36">
-        <v>77.4880217592</v>
+        <v>77.08066945799999</v>
       </c>
       <c r="Q36">
-        <v>84.5880217592</v>
+        <v>84.180669458</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1057386553400446</v>
+        <v>0.1065160698061931</v>
       </c>
       <c r="T36">
-        <v>0.7812016115227075</v>
+        <v>0.7913339281442731</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.594811804897402</v>
+        <v>6.406388610471761</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08405934537402548</v>
+        <v>0.08393081822362151</v>
       </c>
       <c r="C37">
-        <v>651.9626284275862</v>
+        <v>643.1393307038218</v>
       </c>
       <c r="D37">
-        <v>730.7856284275863</v>
+        <v>731.5801307038217</v>
       </c>
       <c r="E37">
-        <v>334.943</v>
+        <v>344.5608</v>
       </c>
       <c r="F37">
-        <v>336.623</v>
+        <v>346.2408</v>
       </c>
       <c r="G37">
         <v>257.8</v>
@@ -4321,28 +4321,28 @@
         <v>117.1</v>
       </c>
       <c r="M37">
-        <v>18.2786289</v>
+        <v>18.80087544</v>
       </c>
       <c r="N37">
-        <v>98.82137109999999</v>
+        <v>98.29912456</v>
       </c>
       <c r="O37">
-        <v>21.740701642</v>
+        <v>21.6258074032</v>
       </c>
       <c r="P37">
-        <v>77.08066945799999</v>
+        <v>76.6733171568</v>
       </c>
       <c r="Q37">
-        <v>84.180669458</v>
+        <v>83.7733171568</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1065160698061931</v>
+        <v>0.1073177784744086</v>
       </c>
       <c r="T37">
-        <v>0.7913339281442731</v>
+        <v>0.8017828796602626</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.406388610471761</v>
+        <v>6.228433371291991</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08393081822362153</v>
+        <v>0.08409089107321757</v>
       </c>
       <c r="C38">
-        <v>643.1393307038218</v>
+        <v>632.5322894995047</v>
       </c>
       <c r="D38">
-        <v>731.5801307038217</v>
+        <v>730.5908894995048</v>
       </c>
       <c r="E38">
-        <v>344.5608</v>
+        <v>354.1786</v>
       </c>
       <c r="F38">
-        <v>346.2408</v>
+        <v>355.8586</v>
       </c>
       <c r="G38">
         <v>257.8</v>
@@ -4403,45 +4403,45 @@
         <v>117.1</v>
       </c>
       <c r="M38">
-        <v>18.80087544</v>
+        <v>19.67898058</v>
       </c>
       <c r="N38">
-        <v>98.29912456</v>
+        <v>97.42101941999999</v>
       </c>
       <c r="O38">
-        <v>21.6258074032</v>
+        <v>21.4326242724</v>
       </c>
       <c r="P38">
-        <v>76.6733171568</v>
+        <v>75.98839514759999</v>
       </c>
       <c r="Q38">
-        <v>83.7733171568</v>
+        <v>83.0883951476</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1073177784744086</v>
+        <v>0.1081449382114565</v>
       </c>
       <c r="T38">
-        <v>0.8017828796602625</v>
+        <v>0.8125635439227914</v>
       </c>
       <c r="U38">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V38">
         <v>0.22</v>
       </c>
       <c r="W38">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>6.228433371291992</v>
+        <v>5.95051148731811</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08409089107321757</v>
+        <v>0.08397016392281362</v>
       </c>
       <c r="C39">
-        <v>632.5322894995047</v>
+        <v>623.6603282675392</v>
       </c>
       <c r="D39">
-        <v>730.5908894995048</v>
+        <v>731.3367282675392</v>
       </c>
       <c r="E39">
-        <v>354.1786</v>
+        <v>363.7964</v>
       </c>
       <c r="F39">
-        <v>355.8586</v>
+        <v>365.4764</v>
       </c>
       <c r="G39">
         <v>257.8</v>
@@ -4485,28 +4485,28 @@
         <v>117.1</v>
       </c>
       <c r="M39">
-        <v>19.67898058</v>
+        <v>20.21084492</v>
       </c>
       <c r="N39">
-        <v>97.42101941999999</v>
+        <v>96.88915507999999</v>
       </c>
       <c r="O39">
-        <v>21.4326242724</v>
+        <v>21.3156141176</v>
       </c>
       <c r="P39">
-        <v>75.98839514759999</v>
+        <v>75.57354096239999</v>
       </c>
       <c r="Q39">
-        <v>83.0883951476</v>
+        <v>82.6735409624</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1081449382114565</v>
+        <v>0.1089987805206671</v>
       </c>
       <c r="T39">
-        <v>0.8125635439227914</v>
+        <v>0.8236919715486276</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.95051148731811</v>
+        <v>5.793919079757106</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08397016392281362</v>
+        <v>0.08384943677240964</v>
       </c>
       <c r="C40">
-        <v>623.6603282675392</v>
+        <v>614.7898914015127</v>
       </c>
       <c r="D40">
-        <v>731.3367282675392</v>
+        <v>732.0840914015126</v>
       </c>
       <c r="E40">
-        <v>363.7964</v>
+        <v>373.4142</v>
       </c>
       <c r="F40">
-        <v>365.4764</v>
+        <v>375.0942</v>
       </c>
       <c r="G40">
         <v>257.8</v>
@@ -4567,28 +4567,28 @@
         <v>117.1</v>
       </c>
       <c r="M40">
-        <v>20.21084492</v>
+        <v>20.74270926</v>
       </c>
       <c r="N40">
-        <v>96.88915507999999</v>
+        <v>96.35729074</v>
       </c>
       <c r="O40">
-        <v>21.3156141176</v>
+        <v>21.1986039628</v>
       </c>
       <c r="P40">
-        <v>75.57354096239999</v>
+        <v>75.15868677719999</v>
       </c>
       <c r="Q40">
-        <v>82.6735409624</v>
+        <v>82.2586867772</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1089987805206671</v>
+        <v>0.1098806176596879</v>
       </c>
       <c r="T40">
-        <v>0.8236919715486276</v>
+        <v>0.8351852656539995</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.793919079757106</v>
+        <v>5.645357052071026</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08384943677240964</v>
+        <v>0.08372870962200568</v>
       </c>
       <c r="C41">
-        <v>614.7898914015127</v>
+        <v>605.920983579517</v>
       </c>
       <c r="D41">
-        <v>732.0840914015126</v>
+        <v>732.8329835795171</v>
       </c>
       <c r="E41">
-        <v>373.4142</v>
+        <v>383.032</v>
       </c>
       <c r="F41">
-        <v>375.0942</v>
+        <v>384.712</v>
       </c>
       <c r="G41">
         <v>257.8</v>
@@ -4649,28 +4649,28 @@
         <v>117.1</v>
       </c>
       <c r="M41">
-        <v>20.74270926</v>
+        <v>21.2745736</v>
       </c>
       <c r="N41">
-        <v>96.35729074</v>
+        <v>95.8254264</v>
       </c>
       <c r="O41">
-        <v>21.1986039628</v>
+        <v>21.081593808</v>
       </c>
       <c r="P41">
-        <v>75.15868677719999</v>
+        <v>74.74383259199999</v>
       </c>
       <c r="Q41">
-        <v>82.2586867772</v>
+        <v>81.843832592</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1098806176596879</v>
+        <v>0.1107918493700095</v>
       </c>
       <c r="T41">
-        <v>0.8351852656539995</v>
+        <v>0.8470616695628839</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.645357052071026</v>
+        <v>5.504223125769252</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08372870962200568</v>
+        <v>0.08360798247160173</v>
       </c>
       <c r="C42">
-        <v>605.920983579517</v>
+        <v>597.053609498807</v>
       </c>
       <c r="D42">
-        <v>732.8329835795171</v>
+        <v>733.583409498807</v>
       </c>
       <c r="E42">
-        <v>383.032</v>
+        <v>392.6498</v>
       </c>
       <c r="F42">
-        <v>384.712</v>
+        <v>394.3298</v>
       </c>
       <c r="G42">
         <v>257.8</v>
@@ -4731,28 +4731,28 @@
         <v>117.1</v>
       </c>
       <c r="M42">
-        <v>21.2745736</v>
+        <v>21.80643794</v>
       </c>
       <c r="N42">
-        <v>95.8254264</v>
+        <v>95.29356206</v>
       </c>
       <c r="O42">
-        <v>21.081593808</v>
+        <v>20.9645836532</v>
       </c>
       <c r="P42">
-        <v>74.74383259199999</v>
+        <v>74.3289784068</v>
       </c>
       <c r="Q42">
-        <v>81.843832592</v>
+        <v>81.42897840680001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1107918493700095</v>
+        <v>0.1117339702908504</v>
       </c>
       <c r="T42">
-        <v>0.8470616695628839</v>
+        <v>0.8593406634347811</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.504223125769252</v>
+        <v>5.369973781238293</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08360798247160173</v>
+        <v>0.08348725532119775</v>
       </c>
       <c r="C43">
-        <v>597.053609498807</v>
+        <v>588.1877738758965</v>
       </c>
       <c r="D43">
-        <v>733.583409498807</v>
+        <v>734.3353738758965</v>
       </c>
       <c r="E43">
-        <v>392.6498</v>
+        <v>402.2676</v>
       </c>
       <c r="F43">
-        <v>394.3298</v>
+        <v>403.9476</v>
       </c>
       <c r="G43">
         <v>257.8</v>
@@ -4813,28 +4813,28 @@
         <v>117.1</v>
       </c>
       <c r="M43">
-        <v>21.80643794</v>
+        <v>22.33830228</v>
       </c>
       <c r="N43">
-        <v>95.29356206</v>
+        <v>94.76169772</v>
       </c>
       <c r="O43">
-        <v>20.9645836532</v>
+        <v>20.8475734984</v>
       </c>
       <c r="P43">
-        <v>74.3289784068</v>
+        <v>73.91412422160001</v>
       </c>
       <c r="Q43">
-        <v>81.42897840680001</v>
+        <v>81.01412422160001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1117339702908504</v>
+        <v>0.1127085781399961</v>
       </c>
       <c r="T43">
-        <v>0.8593406634347811</v>
+        <v>0.872043070888468</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.369973781238293</v>
+        <v>5.242117262637382</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08348725532119776</v>
+        <v>0.0833665281707938</v>
       </c>
       <c r="C44">
-        <v>588.1877738758965</v>
+        <v>579.323481446658</v>
       </c>
       <c r="D44">
-        <v>734.3353738758965</v>
+        <v>735.0888814466579</v>
       </c>
       <c r="E44">
-        <v>402.2676</v>
+        <v>411.8853999999999</v>
       </c>
       <c r="F44">
-        <v>403.9476</v>
+        <v>413.5654</v>
       </c>
       <c r="G44">
         <v>257.8</v>
@@ -4895,28 +4895,28 @@
         <v>117.1</v>
       </c>
       <c r="M44">
-        <v>22.33830228</v>
+        <v>22.87016662</v>
       </c>
       <c r="N44">
-        <v>94.76169772</v>
+        <v>94.22983338</v>
       </c>
       <c r="O44">
-        <v>20.8475734984</v>
+        <v>20.7305633436</v>
       </c>
       <c r="P44">
-        <v>73.91412422160001</v>
+        <v>73.49927003640001</v>
       </c>
       <c r="Q44">
-        <v>81.01412422160001</v>
+        <v>80.59927003640001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1127085781399961</v>
+        <v>0.1137173827557786</v>
       </c>
       <c r="T44">
-        <v>0.872043070888468</v>
+        <v>0.8851911768493017</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.242117262637382</v>
+        <v>5.120207558855118</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0833665281707938</v>
+        <v>0.08324580102038986</v>
       </c>
       <c r="C45">
-        <v>579.323481446658</v>
+        <v>570.460736966422</v>
       </c>
       <c r="D45">
-        <v>735.0888814466579</v>
+        <v>735.843936966422</v>
       </c>
       <c r="E45">
-        <v>411.8853999999999</v>
+        <v>421.5032</v>
       </c>
       <c r="F45">
-        <v>413.5654</v>
+        <v>423.1832</v>
       </c>
       <c r="G45">
         <v>257.8</v>
@@ -4977,28 +4977,28 @@
         <v>117.1</v>
       </c>
       <c r="M45">
-        <v>22.87016662</v>
+        <v>23.40203096</v>
       </c>
       <c r="N45">
-        <v>94.22983338</v>
+        <v>93.69796903999999</v>
       </c>
       <c r="O45">
-        <v>20.7305633436</v>
+        <v>20.6135531888</v>
       </c>
       <c r="P45">
-        <v>73.49927003640001</v>
+        <v>73.08441585119999</v>
       </c>
       <c r="Q45">
-        <v>80.59927003640001</v>
+        <v>80.1844158512</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1137173827557786</v>
+        <v>0.114762216107839</v>
       </c>
       <c r="T45">
-        <v>0.8851911768493017</v>
+        <v>0.8988088580230225</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.120207558855118</v>
+        <v>5.003839205244773</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08324580102038986</v>
+        <v>0.08312507386998588</v>
       </c>
       <c r="C46">
-        <v>570.460736966422</v>
+        <v>561.5995452100781</v>
       </c>
       <c r="D46">
-        <v>735.843936966422</v>
+        <v>736.6005452100779</v>
       </c>
       <c r="E46">
-        <v>421.5032</v>
+        <v>431.121</v>
       </c>
       <c r="F46">
-        <v>423.1832</v>
+        <v>432.801</v>
       </c>
       <c r="G46">
         <v>257.8</v>
@@ -5059,28 +5059,28 @@
         <v>117.1</v>
       </c>
       <c r="M46">
-        <v>23.40203096</v>
+        <v>23.9338953</v>
       </c>
       <c r="N46">
-        <v>93.69796903999999</v>
+        <v>93.16610469999999</v>
       </c>
       <c r="O46">
-        <v>20.6135531888</v>
+        <v>20.496543034</v>
       </c>
       <c r="P46">
-        <v>73.08441585119999</v>
+        <v>72.66956166599999</v>
       </c>
       <c r="Q46">
-        <v>80.1844158512</v>
+        <v>79.769561666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.114762216107839</v>
+        <v>0.1158450433999743</v>
       </c>
       <c r="T46">
-        <v>0.8988088580230225</v>
+        <v>0.9129217276030602</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.003839205244773</v>
+        <v>4.892642778461557</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08312507386998588</v>
+        <v>0.08300434671958193</v>
       </c>
       <c r="C47">
-        <v>561.5995452100781</v>
+        <v>552.7399109721724</v>
       </c>
       <c r="D47">
-        <v>736.6005452100779</v>
+        <v>737.3587109721725</v>
       </c>
       <c r="E47">
-        <v>431.121</v>
+        <v>440.7388</v>
       </c>
       <c r="F47">
-        <v>432.801</v>
+        <v>442.4188</v>
       </c>
       <c r="G47">
         <v>257.8</v>
@@ -5141,28 +5141,28 @@
         <v>117.1</v>
       </c>
       <c r="M47">
-        <v>23.9338953</v>
+        <v>24.46575964</v>
       </c>
       <c r="N47">
-        <v>93.16610469999999</v>
+        <v>92.63424035999999</v>
       </c>
       <c r="O47">
-        <v>20.496543034</v>
+        <v>20.3795328792</v>
       </c>
       <c r="P47">
-        <v>72.66956166599999</v>
+        <v>72.25470748079999</v>
       </c>
       <c r="Q47">
-        <v>79.769561666</v>
+        <v>79.3547074808</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1158450433999743</v>
+        <v>0.1169679754066332</v>
       </c>
       <c r="T47">
-        <v>0.9129217276030602</v>
+        <v>0.9275572960564327</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.892642778461557</v>
+        <v>4.786280978929783</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08300434671958193</v>
+        <v>0.08288361956917797</v>
       </c>
       <c r="C48">
-        <v>552.7399109721724</v>
+        <v>543.8818390670136</v>
       </c>
       <c r="D48">
-        <v>737.3587109721725</v>
+        <v>738.1184390670136</v>
       </c>
       <c r="E48">
-        <v>440.7388</v>
+        <v>450.3566</v>
       </c>
       <c r="F48">
-        <v>442.4188</v>
+        <v>452.0366</v>
       </c>
       <c r="G48">
         <v>257.8</v>
@@ -5223,28 +5223,28 @@
         <v>117.1</v>
       </c>
       <c r="M48">
-        <v>24.46575964</v>
+        <v>24.99762398</v>
       </c>
       <c r="N48">
-        <v>92.63424035999999</v>
+        <v>92.10237601999999</v>
       </c>
       <c r="O48">
-        <v>20.3795328792</v>
+        <v>20.2625227244</v>
       </c>
       <c r="P48">
-        <v>72.25470748079999</v>
+        <v>71.83985329559999</v>
       </c>
       <c r="Q48">
-        <v>79.3547074808</v>
+        <v>78.9398532956</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1169679754066332</v>
+        <v>0.1181332822059961</v>
       </c>
       <c r="T48">
-        <v>0.9275572960564327</v>
+        <v>0.9427451501118194</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.786280978929783</v>
+        <v>4.684445213420639</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08288361956917797</v>
+        <v>0.08276289241877401</v>
       </c>
       <c r="C49">
-        <v>543.8818390670136</v>
+        <v>535.0253343287706</v>
       </c>
       <c r="D49">
-        <v>738.1184390670136</v>
+        <v>738.8797343287706</v>
       </c>
       <c r="E49">
-        <v>450.3566</v>
+        <v>459.9744</v>
       </c>
       <c r="F49">
-        <v>452.0366</v>
+        <v>461.6544</v>
       </c>
       <c r="G49">
         <v>257.8</v>
@@ -5305,28 +5305,28 @@
         <v>117.1</v>
       </c>
       <c r="M49">
-        <v>24.99762398</v>
+        <v>25.52948832</v>
       </c>
       <c r="N49">
-        <v>92.10237601999999</v>
+        <v>91.57051168</v>
       </c>
       <c r="O49">
-        <v>20.2625227244</v>
+        <v>20.1455125696</v>
       </c>
       <c r="P49">
-        <v>71.83985329559999</v>
+        <v>71.42499911039999</v>
       </c>
       <c r="Q49">
-        <v>78.9398532956</v>
+        <v>78.5249991104</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1181332822059961</v>
+        <v>0.1193434084976423</v>
       </c>
       <c r="T49">
-        <v>0.9427451501118194</v>
+        <v>0.9585171524001055</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.684445213420639</v>
+        <v>4.586852604807709</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08276289241877401</v>
+        <v>0.08359766526837004</v>
       </c>
       <c r="C50">
-        <v>535.0253343287707</v>
+        <v>520.1754113220314</v>
       </c>
       <c r="D50">
-        <v>738.8797343287706</v>
+        <v>733.6476113220315</v>
       </c>
       <c r="E50">
-        <v>459.9743999999999</v>
+        <v>469.5922</v>
       </c>
       <c r="F50">
-        <v>461.6544</v>
+        <v>471.2722</v>
       </c>
       <c r="G50">
         <v>257.8</v>
@@ -5387,45 +5387,45 @@
         <v>117.1</v>
       </c>
       <c r="M50">
-        <v>25.52948832</v>
+        <v>27.23953316</v>
       </c>
       <c r="N50">
-        <v>91.57051168</v>
+        <v>89.86046683999999</v>
       </c>
       <c r="O50">
-        <v>20.1455125696</v>
+        <v>19.7693027048</v>
       </c>
       <c r="P50">
-        <v>71.42499911039999</v>
+        <v>70.09116413519999</v>
       </c>
       <c r="Q50">
-        <v>78.5249991104</v>
+        <v>77.1911641352</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1193434084976423</v>
+        <v>0.1206009907222942</v>
       </c>
       <c r="T50">
-        <v>0.9585171524001054</v>
+        <v>0.9749076645820498</v>
       </c>
       <c r="U50">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.58685260480771</v>
+        <v>4.298898931643805</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08359766526837004</v>
+        <v>0.08349643811796607</v>
       </c>
       <c r="C51">
-        <v>520.1754113220314</v>
+        <v>511.1881234952535</v>
       </c>
       <c r="D51">
-        <v>733.6476113220315</v>
+        <v>734.2781234952535</v>
       </c>
       <c r="E51">
-        <v>469.5922</v>
+        <v>479.21</v>
       </c>
       <c r="F51">
-        <v>471.2722</v>
+        <v>480.89</v>
       </c>
       <c r="G51">
         <v>257.8</v>
@@ -5469,28 +5469,28 @@
         <v>117.1</v>
       </c>
       <c r="M51">
-        <v>27.23953316</v>
+        <v>27.795442</v>
       </c>
       <c r="N51">
-        <v>89.86046683999999</v>
+        <v>89.30455799999999</v>
       </c>
       <c r="O51">
-        <v>19.7693027048</v>
+        <v>19.64700276</v>
       </c>
       <c r="P51">
-        <v>70.09116413519999</v>
+        <v>69.65755523999999</v>
       </c>
       <c r="Q51">
-        <v>77.1911641352</v>
+        <v>76.75755524</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1206009907222942</v>
+        <v>0.1219088762359321</v>
       </c>
       <c r="T51">
-        <v>0.9749076645820498</v>
+        <v>0.9919537972512719</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.298898931643805</v>
+        <v>4.212920953010928</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08349643811796607</v>
+        <v>0.08339521096756211</v>
       </c>
       <c r="C52">
-        <v>511.1881234952535</v>
+        <v>502.2019203514959</v>
       </c>
       <c r="D52">
-        <v>734.2781234952535</v>
+        <v>734.9097203514958</v>
       </c>
       <c r="E52">
-        <v>479.21</v>
+        <v>488.8278</v>
       </c>
       <c r="F52">
-        <v>480.89</v>
+        <v>490.5078</v>
       </c>
       <c r="G52">
         <v>257.8</v>
@@ -5551,28 +5551,28 @@
         <v>117.1</v>
       </c>
       <c r="M52">
-        <v>27.795442</v>
+        <v>28.35135084</v>
       </c>
       <c r="N52">
-        <v>89.30455799999999</v>
+        <v>88.74864915999999</v>
       </c>
       <c r="O52">
-        <v>19.64700276</v>
+        <v>19.5247028152</v>
       </c>
       <c r="P52">
-        <v>69.65755523999999</v>
+        <v>69.22394634479998</v>
       </c>
       <c r="Q52">
-        <v>76.75755524</v>
+        <v>76.32394634479999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1219088762359321</v>
+        <v>0.1232701448317594</v>
       </c>
       <c r="T52">
-        <v>0.9919537972512719</v>
+        <v>1.009695690437605</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.212920953010928</v>
+        <v>4.130314659814635</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08339521096756211</v>
+        <v>0.08329398381715816</v>
       </c>
       <c r="C53">
-        <v>502.2019203514959</v>
+        <v>493.2168046921716</v>
       </c>
       <c r="D53">
-        <v>734.9097203514958</v>
+        <v>735.5424046921717</v>
       </c>
       <c r="E53">
-        <v>488.8278</v>
+        <v>498.4456</v>
       </c>
       <c r="F53">
-        <v>490.5078</v>
+        <v>500.1256</v>
       </c>
       <c r="G53">
         <v>257.8</v>
@@ -5633,28 +5633,28 @@
         <v>117.1</v>
       </c>
       <c r="M53">
-        <v>28.35135084</v>
+        <v>28.90725968</v>
       </c>
       <c r="N53">
-        <v>88.74864915999999</v>
+        <v>88.19274031999998</v>
       </c>
       <c r="O53">
-        <v>19.5247028152</v>
+        <v>19.4024028704</v>
       </c>
       <c r="P53">
-        <v>69.22394634479998</v>
+        <v>68.79033744959999</v>
       </c>
       <c r="Q53">
-        <v>76.32394634479999</v>
+        <v>75.8903374496</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1232701448317594</v>
+        <v>0.1246881329524128</v>
       </c>
       <c r="T53">
-        <v>1.009695690437605</v>
+        <v>1.028176829173369</v>
       </c>
       <c r="U53">
         <v>0.0578</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.130314659814635</v>
+        <v>4.050885531741277</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08329398381715816</v>
+        <v>0.08463965666675419</v>
       </c>
       <c r="C54">
-        <v>493.2168046921716</v>
+        <v>475.2763620961258</v>
       </c>
       <c r="D54">
-        <v>735.5424046921717</v>
+        <v>727.2197620961257</v>
       </c>
       <c r="E54">
-        <v>498.4456</v>
+        <v>508.0634</v>
       </c>
       <c r="F54">
-        <v>500.1256</v>
+        <v>509.7434</v>
       </c>
       <c r="G54">
         <v>257.8</v>
@@ -5715,45 +5715,45 @@
         <v>117.1</v>
       </c>
       <c r="M54">
-        <v>28.90725968</v>
+        <v>31.24727042</v>
       </c>
       <c r="N54">
-        <v>88.19274031999998</v>
+        <v>85.85272957999999</v>
       </c>
       <c r="O54">
-        <v>19.4024028704</v>
+        <v>18.8876005076</v>
       </c>
       <c r="P54">
-        <v>68.79033744959999</v>
+        <v>66.96512907239999</v>
       </c>
       <c r="Q54">
-        <v>75.8903374496</v>
+        <v>74.0651290724</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1246881329524128</v>
+        <v>0.126166460993094</v>
       </c>
       <c r="T54">
-        <v>1.028176829173369</v>
+        <v>1.047444399344697</v>
       </c>
       <c r="U54">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V54">
         <v>0.22</v>
       </c>
       <c r="W54">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y54">
-        <v>4.050885531741277</v>
+        <v>3.747527333621097</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08463965666675419</v>
+        <v>0.08456572951635023</v>
       </c>
       <c r="C55">
-        <v>475.2763620961258</v>
+        <v>466.1108903579939</v>
       </c>
       <c r="D55">
-        <v>727.2197620961257</v>
+        <v>727.6720903579939</v>
       </c>
       <c r="E55">
-        <v>508.0634</v>
+        <v>517.6812000000001</v>
       </c>
       <c r="F55">
-        <v>509.7434</v>
+        <v>519.3612000000001</v>
       </c>
       <c r="G55">
         <v>257.8</v>
@@ -5797,28 +5797,28 @@
         <v>117.1</v>
       </c>
       <c r="M55">
-        <v>31.24727042</v>
+        <v>31.83684156</v>
       </c>
       <c r="N55">
-        <v>85.85272957999999</v>
+        <v>85.26315843999998</v>
       </c>
       <c r="O55">
-        <v>18.8876005076</v>
+        <v>18.7578948568</v>
       </c>
       <c r="P55">
-        <v>66.96512907239999</v>
+        <v>66.50526358319999</v>
       </c>
       <c r="Q55">
-        <v>74.0651290724</v>
+        <v>73.6052635832</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.126166460993094</v>
+        <v>0.1277090641659788</v>
       </c>
       <c r="T55">
-        <v>1.047444399344697</v>
+        <v>1.067549689958257</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.747527333621097</v>
+        <v>3.67812867929478</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08456572951635023</v>
+        <v>0.08449180236594628</v>
       </c>
       <c r="C56">
-        <v>466.1108903579939</v>
+        <v>456.945981663408</v>
       </c>
       <c r="D56">
-        <v>727.6720903579939</v>
+        <v>728.124981663408</v>
       </c>
       <c r="E56">
-        <v>517.6812000000001</v>
+        <v>527.2990000000001</v>
       </c>
       <c r="F56">
-        <v>519.3612000000001</v>
+        <v>528.979</v>
       </c>
       <c r="G56">
         <v>257.8</v>
@@ -5879,28 +5879,28 @@
         <v>117.1</v>
       </c>
       <c r="M56">
-        <v>31.83684156</v>
+        <v>32.4264127</v>
       </c>
       <c r="N56">
-        <v>85.26315843999998</v>
+        <v>84.67358729999999</v>
       </c>
       <c r="O56">
-        <v>18.7578948568</v>
+        <v>18.628189206</v>
       </c>
       <c r="P56">
-        <v>66.50526358319999</v>
+        <v>66.04539809399999</v>
       </c>
       <c r="Q56">
-        <v>73.6052635832</v>
+        <v>73.145398094</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1277090641659788</v>
+        <v>0.1293202274798806</v>
       </c>
       <c r="T56">
-        <v>1.067549689958257</v>
+        <v>1.088548549043531</v>
       </c>
       <c r="U56">
         <v>0.0613</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.67812867929478</v>
+        <v>3.611253612398512</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08449180236594628</v>
+        <v>0.08441787521554231</v>
       </c>
       <c r="C57">
-        <v>456.945981663408</v>
+        <v>447.7816370643102</v>
       </c>
       <c r="D57">
-        <v>728.124981663408</v>
+        <v>728.5784370643103</v>
       </c>
       <c r="E57">
-        <v>527.2990000000001</v>
+        <v>536.9168000000001</v>
       </c>
       <c r="F57">
-        <v>528.979</v>
+        <v>538.5968</v>
       </c>
       <c r="G57">
         <v>257.8</v>
@@ -5961,28 +5961,28 @@
         <v>117.1</v>
       </c>
       <c r="M57">
-        <v>32.4264127</v>
+        <v>33.01598384</v>
       </c>
       <c r="N57">
-        <v>84.67358729999999</v>
+        <v>84.08401615999999</v>
       </c>
       <c r="O57">
-        <v>18.628189206</v>
+        <v>18.4984835552</v>
       </c>
       <c r="P57">
-        <v>66.04539809399999</v>
+        <v>65.58553260479999</v>
       </c>
       <c r="Q57">
-        <v>73.145398094</v>
+        <v>72.6855326048</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1293202274798806</v>
+        <v>0.1310046254898689</v>
       </c>
       <c r="T57">
-        <v>1.088548549043531</v>
+        <v>1.110501901723589</v>
       </c>
       <c r="U57">
         <v>0.0613</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.611253612398512</v>
+        <v>3.546766940748538</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08441787521554231</v>
+        <v>0.08558882806513834</v>
       </c>
       <c r="C58">
-        <v>447.7816370643102</v>
+        <v>431.0471576219802</v>
       </c>
       <c r="D58">
-        <v>728.5784370643103</v>
+        <v>721.4617576219803</v>
       </c>
       <c r="E58">
-        <v>536.9168000000001</v>
+        <v>546.5346000000001</v>
       </c>
       <c r="F58">
-        <v>538.5968</v>
+        <v>548.2146</v>
       </c>
       <c r="G58">
         <v>257.8</v>
@@ -6043,45 +6043,45 @@
         <v>117.1</v>
       </c>
       <c r="M58">
-        <v>33.01598384</v>
+        <v>35.14055586000001</v>
       </c>
       <c r="N58">
-        <v>84.08401615999999</v>
+        <v>81.95944413999999</v>
       </c>
       <c r="O58">
-        <v>18.4984835552</v>
+        <v>18.0310777108</v>
       </c>
       <c r="P58">
-        <v>65.58553260479999</v>
+        <v>63.92836642919999</v>
       </c>
       <c r="Q58">
-        <v>72.6855326048</v>
+        <v>71.02836642919999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1310046254898689</v>
+        <v>0.132767367593345</v>
       </c>
       <c r="T58">
-        <v>1.110501901723589</v>
+        <v>1.133476340574814</v>
       </c>
       <c r="U58">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V58">
         <v>0.22</v>
       </c>
       <c r="W58">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>3.546766940748538</v>
+        <v>3.332332034431284</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08558882806513834</v>
+        <v>0.08553674091473439</v>
       </c>
       <c r="C59">
-        <v>431.0471576219802</v>
+        <v>421.7429708262698</v>
       </c>
       <c r="D59">
-        <v>721.4617576219803</v>
+        <v>721.7753708262698</v>
       </c>
       <c r="E59">
-        <v>546.5346000000001</v>
+        <v>556.1524000000001</v>
       </c>
       <c r="F59">
-        <v>548.2146</v>
+        <v>557.8324</v>
       </c>
       <c r="G59">
         <v>257.8</v>
@@ -6125,28 +6125,28 @@
         <v>117.1</v>
       </c>
       <c r="M59">
-        <v>35.14055586000001</v>
+        <v>35.75705684</v>
       </c>
       <c r="N59">
-        <v>81.95944413999999</v>
+        <v>81.34294315999999</v>
       </c>
       <c r="O59">
-        <v>18.0310777108</v>
+        <v>17.8954474952</v>
       </c>
       <c r="P59">
-        <v>63.92836642919999</v>
+        <v>63.44749566479999</v>
       </c>
       <c r="Q59">
-        <v>71.02836642919999</v>
+        <v>70.5474956648</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.132767367593345</v>
+        <v>0.1346140497969866</v>
       </c>
       <c r="T59">
-        <v>1.133476340574814</v>
+        <v>1.157544800323715</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.332332034431284</v>
+        <v>3.274878033837641</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08553674091473439</v>
+        <v>0.08548465376433043</v>
       </c>
       <c r="C60">
-        <v>421.7429708262699</v>
+        <v>412.4390567990399</v>
       </c>
       <c r="D60">
-        <v>721.7753708262698</v>
+        <v>722.08925679904</v>
       </c>
       <c r="E60">
-        <v>556.1523999999999</v>
+        <v>565.7702</v>
       </c>
       <c r="F60">
-        <v>557.8323999999999</v>
+        <v>567.4502</v>
       </c>
       <c r="G60">
         <v>257.8</v>
@@ -6207,28 +6207,28 @@
         <v>117.1</v>
       </c>
       <c r="M60">
-        <v>35.75705684</v>
+        <v>36.37355782</v>
       </c>
       <c r="N60">
-        <v>81.34294316</v>
+        <v>80.72644217999999</v>
       </c>
       <c r="O60">
-        <v>17.8954474952</v>
+        <v>17.7598172796</v>
       </c>
       <c r="P60">
-        <v>63.4474956648</v>
+        <v>62.96662490039999</v>
       </c>
       <c r="Q60">
-        <v>70.54749566480001</v>
+        <v>70.0666249004</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1346140497969866</v>
+        <v>0.1365508140593425</v>
       </c>
       <c r="T60">
-        <v>1.157544800323715</v>
+        <v>1.18278733127988</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.274878033837642</v>
+        <v>3.219371626484461</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08548465376433043</v>
+        <v>0.08543256661392647</v>
       </c>
       <c r="C61">
-        <v>412.4390567990399</v>
+        <v>403.1354158963111</v>
       </c>
       <c r="D61">
-        <v>722.08925679904</v>
+        <v>722.403415896311</v>
       </c>
       <c r="E61">
-        <v>565.7702</v>
+        <v>575.388</v>
       </c>
       <c r="F61">
-        <v>567.4502</v>
+        <v>577.068</v>
       </c>
       <c r="G61">
         <v>257.8</v>
@@ -6289,28 +6289,28 @@
         <v>117.1</v>
       </c>
       <c r="M61">
-        <v>36.37355782</v>
+        <v>36.9900588</v>
       </c>
       <c r="N61">
-        <v>80.72644217999999</v>
+        <v>80.10994119999999</v>
       </c>
       <c r="O61">
-        <v>17.7598172796</v>
+        <v>17.624187064</v>
       </c>
       <c r="P61">
-        <v>62.96662490039999</v>
+        <v>62.485754136</v>
       </c>
       <c r="Q61">
-        <v>70.0666249004</v>
+        <v>69.58575413600001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1365508140593425</v>
+        <v>0.1385844165348162</v>
       </c>
       <c r="T61">
-        <v>1.18278733127988</v>
+        <v>1.209291988783854</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.219371626484461</v>
+        <v>3.16571543270972</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08543256661392647</v>
+        <v>0.08538047946352249</v>
       </c>
       <c r="C62">
-        <v>403.1354158963111</v>
+        <v>393.8320484747226</v>
       </c>
       <c r="D62">
-        <v>722.403415896311</v>
+        <v>722.7178484747225</v>
       </c>
       <c r="E62">
-        <v>575.388</v>
+        <v>585.0058</v>
       </c>
       <c r="F62">
-        <v>577.068</v>
+        <v>586.6858</v>
       </c>
       <c r="G62">
         <v>257.8</v>
@@ -6371,28 +6371,28 @@
         <v>117.1</v>
       </c>
       <c r="M62">
-        <v>36.9900588</v>
+        <v>37.60655978</v>
       </c>
       <c r="N62">
-        <v>80.10994119999999</v>
+        <v>79.49344022</v>
       </c>
       <c r="O62">
-        <v>17.624187064</v>
+        <v>17.4885568484</v>
       </c>
       <c r="P62">
-        <v>62.485754136</v>
+        <v>62.0048833716</v>
       </c>
       <c r="Q62">
-        <v>69.58575413600001</v>
+        <v>69.10488337160001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1385844165348162</v>
+        <v>0.1407223063167243</v>
       </c>
       <c r="T62">
-        <v>1.209291988783854</v>
+        <v>1.237155859493159</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.16571543270972</v>
+        <v>3.113818458403004</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08538047946352249</v>
+        <v>0.08532839231311853</v>
       </c>
       <c r="C63">
-        <v>393.8320484747226</v>
+        <v>384.528954891535</v>
       </c>
       <c r="D63">
-        <v>722.7178484747225</v>
+        <v>723.032554891535</v>
       </c>
       <c r="E63">
-        <v>585.0058</v>
+        <v>594.6236</v>
       </c>
       <c r="F63">
-        <v>586.6858</v>
+        <v>596.3036</v>
       </c>
       <c r="G63">
         <v>257.8</v>
@@ -6453,28 +6453,28 @@
         <v>117.1</v>
       </c>
       <c r="M63">
-        <v>37.60655978</v>
+        <v>38.22306076</v>
       </c>
       <c r="N63">
-        <v>79.49344022</v>
+        <v>78.87693923999998</v>
       </c>
       <c r="O63">
-        <v>17.4885568484</v>
+        <v>17.3529266328</v>
       </c>
       <c r="P63">
-        <v>62.0048833716</v>
+        <v>61.52401260719999</v>
       </c>
       <c r="Q63">
-        <v>69.10488337160001</v>
+        <v>68.6240126072</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1407223063167243</v>
+        <v>0.1429727166134698</v>
       </c>
       <c r="T63">
-        <v>1.237155859493159</v>
+        <v>1.266486249713481</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.113818458403004</v>
+        <v>3.063595580041664</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08532839231311853</v>
+        <v>0.08527630516271459</v>
       </c>
       <c r="C64">
-        <v>384.528954891535</v>
+        <v>375.2261355046321</v>
       </c>
       <c r="D64">
-        <v>723.032554891535</v>
+        <v>723.347535504632</v>
       </c>
       <c r="E64">
-        <v>594.6236</v>
+        <v>604.2414</v>
       </c>
       <c r="F64">
-        <v>596.3036</v>
+        <v>605.9213999999999</v>
       </c>
       <c r="G64">
         <v>257.8</v>
@@ -6535,28 +6535,28 @@
         <v>117.1</v>
       </c>
       <c r="M64">
-        <v>38.22306076</v>
+        <v>38.83956174</v>
       </c>
       <c r="N64">
-        <v>78.87693923999998</v>
+        <v>78.26043826</v>
       </c>
       <c r="O64">
-        <v>17.3529266328</v>
+        <v>17.2172964172</v>
       </c>
       <c r="P64">
-        <v>61.52401260719999</v>
+        <v>61.0431418428</v>
       </c>
       <c r="Q64">
-        <v>68.6240126072</v>
+        <v>68.14314184280001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1429727166134698</v>
+        <v>0.1453447707100394</v>
       </c>
       <c r="T64">
-        <v>1.266486249713481</v>
+        <v>1.297402066432198</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.063595580041664</v>
+        <v>3.014967078771162</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08527630516271459</v>
+        <v>0.08911797801231061</v>
       </c>
       <c r="C65">
-        <v>375.2261355046321</v>
+        <v>343.0904192392621</v>
       </c>
       <c r="D65">
-        <v>723.347535504632</v>
+        <v>700.8296192392622</v>
       </c>
       <c r="E65">
-        <v>604.2414</v>
+        <v>613.8592000000001</v>
       </c>
       <c r="F65">
-        <v>605.9213999999999</v>
+        <v>615.5392000000001</v>
       </c>
       <c r="G65">
         <v>257.8</v>
@@ -6617,45 +6617,45 @@
         <v>117.1</v>
       </c>
       <c r="M65">
-        <v>38.83956174</v>
+        <v>44.25726848000001</v>
       </c>
       <c r="N65">
-        <v>78.26043826</v>
+        <v>72.84273151999999</v>
       </c>
       <c r="O65">
-        <v>17.2172964172</v>
+        <v>16.0254009344</v>
       </c>
       <c r="P65">
-        <v>61.0431418428</v>
+        <v>56.81733058559999</v>
       </c>
       <c r="Q65">
-        <v>68.14314184280001</v>
+        <v>63.9173305856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1453447707100394</v>
+        <v>0.1478486055897517</v>
       </c>
       <c r="T65">
-        <v>1.297402066432198</v>
+        <v>1.330035428524177</v>
       </c>
       <c r="U65">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V65">
         <v>0.22</v>
       </c>
       <c r="W65">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.014967078771162</v>
+        <v>2.645893070714878</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08911797801231061</v>
+        <v>0.08912673086190667</v>
       </c>
       <c r="C66">
-        <v>343.0904192392621</v>
+        <v>333.4229151721016</v>
       </c>
       <c r="D66">
-        <v>700.8296192392622</v>
+        <v>700.7799151721017</v>
       </c>
       <c r="E66">
-        <v>613.8592000000001</v>
+        <v>623.4770000000001</v>
       </c>
       <c r="F66">
-        <v>615.5392000000001</v>
+        <v>625.157</v>
       </c>
       <c r="G66">
         <v>257.8</v>
@@ -6699,28 +6699,28 @@
         <v>117.1</v>
       </c>
       <c r="M66">
-        <v>44.25726848000001</v>
+        <v>44.9487883</v>
       </c>
       <c r="N66">
-        <v>72.84273151999999</v>
+        <v>72.15121169999999</v>
       </c>
       <c r="O66">
-        <v>16.0254009344</v>
+        <v>15.873266574</v>
       </c>
       <c r="P66">
-        <v>56.81733058559999</v>
+        <v>56.27794512599999</v>
       </c>
       <c r="Q66">
-        <v>63.9173305856</v>
+        <v>63.377945126</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1478486055897517</v>
+        <v>0.1504955167483047</v>
       </c>
       <c r="T66">
-        <v>1.330035428524177</v>
+        <v>1.36453355416427</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.645893070714878</v>
+        <v>2.60518702347311</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08912673086190667</v>
+        <v>0.08913548371150271</v>
       </c>
       <c r="C67">
-        <v>333.4229151721016</v>
+        <v>323.7554181546406</v>
       </c>
       <c r="D67">
-        <v>700.7799151721017</v>
+        <v>700.7302181546406</v>
       </c>
       <c r="E67">
-        <v>623.4770000000001</v>
+        <v>633.0948000000001</v>
       </c>
       <c r="F67">
-        <v>625.157</v>
+        <v>634.7748</v>
       </c>
       <c r="G67">
         <v>257.8</v>
@@ -6781,28 +6781,28 @@
         <v>117.1</v>
       </c>
       <c r="M67">
-        <v>44.9487883</v>
+        <v>45.64030812000001</v>
       </c>
       <c r="N67">
-        <v>72.15121169999999</v>
+        <v>71.45969187999998</v>
       </c>
       <c r="O67">
-        <v>15.873266574</v>
+        <v>15.7211322136</v>
       </c>
       <c r="P67">
-        <v>56.27794512599999</v>
+        <v>55.73855966639999</v>
       </c>
       <c r="Q67">
-        <v>63.377945126</v>
+        <v>62.83855966639999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1504955167483047</v>
+        <v>0.1532981285632432</v>
       </c>
       <c r="T67">
-        <v>1.36453355416427</v>
+        <v>1.401060981312603</v>
       </c>
       <c r="U67">
         <v>0.07190000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.60518702347311</v>
+        <v>2.565714492814427</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08913548371150271</v>
+        <v>0.08914423656109874</v>
       </c>
       <c r="C68">
-        <v>323.7554181546406</v>
+        <v>314.0879281853794</v>
       </c>
       <c r="D68">
-        <v>700.7302181546406</v>
+        <v>700.6805281853793</v>
       </c>
       <c r="E68">
-        <v>633.0948000000001</v>
+        <v>642.7126000000001</v>
       </c>
       <c r="F68">
-        <v>634.7748</v>
+        <v>644.3926</v>
       </c>
       <c r="G68">
         <v>257.8</v>
@@ -6863,28 +6863,28 @@
         <v>117.1</v>
       </c>
       <c r="M68">
-        <v>45.64030812000001</v>
+        <v>46.33182794</v>
       </c>
       <c r="N68">
-        <v>71.45969187999998</v>
+        <v>70.76817205999998</v>
       </c>
       <c r="O68">
-        <v>15.7211322136</v>
+        <v>15.5689978532</v>
       </c>
       <c r="P68">
-        <v>55.73855966639999</v>
+        <v>55.19917420679999</v>
       </c>
       <c r="Q68">
-        <v>62.83855966639999</v>
+        <v>62.2991742068</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1532981285632432</v>
+        <v>0.1562705956396931</v>
       </c>
       <c r="T68">
-        <v>1.401060981312603</v>
+        <v>1.439802191924471</v>
       </c>
       <c r="U68">
         <v>0.07190000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.565714492814427</v>
+        <v>2.527420246653018</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08914423656109874</v>
+        <v>0.09122154941069478</v>
       </c>
       <c r="C69">
-        <v>314.0879281853794</v>
+        <v>292.8732191813025</v>
       </c>
       <c r="D69">
-        <v>700.6805281853793</v>
+        <v>689.0836191813025</v>
       </c>
       <c r="E69">
-        <v>642.7126000000001</v>
+        <v>652.3304000000001</v>
       </c>
       <c r="F69">
-        <v>644.3926</v>
+        <v>654.0104</v>
       </c>
       <c r="G69">
         <v>257.8</v>
@@ -6945,45 +6945,45 @@
         <v>117.1</v>
       </c>
       <c r="M69">
-        <v>46.33182794</v>
+        <v>49.57398832000001</v>
       </c>
       <c r="N69">
-        <v>70.76817205999998</v>
+        <v>67.52601167999998</v>
       </c>
       <c r="O69">
-        <v>15.5689978532</v>
+        <v>14.8557225696</v>
       </c>
       <c r="P69">
-        <v>55.19917420679999</v>
+        <v>52.67028911039998</v>
       </c>
       <c r="Q69">
-        <v>62.2991742068</v>
+        <v>59.77028911039999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1562705956396931</v>
+        <v>0.1594288419084212</v>
       </c>
       <c r="T69">
-        <v>1.439802191924471</v>
+        <v>1.480964728199582</v>
       </c>
       <c r="U69">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V69">
         <v>0.22</v>
       </c>
       <c r="W69">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.527420246653018</v>
+        <v>2.362125864155204</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09122154941069478</v>
+        <v>0.09126072226029082</v>
       </c>
       <c r="C70">
-        <v>292.8732191813025</v>
+        <v>283.0404174987735</v>
       </c>
       <c r="D70">
-        <v>689.0836191813025</v>
+        <v>688.8686174987735</v>
       </c>
       <c r="E70">
-        <v>652.3304000000001</v>
+        <v>661.9482</v>
       </c>
       <c r="F70">
-        <v>654.0104</v>
+        <v>663.6282</v>
       </c>
       <c r="G70">
         <v>257.8</v>
@@ -7027,28 +7027,28 @@
         <v>117.1</v>
       </c>
       <c r="M70">
-        <v>49.57398832000001</v>
+        <v>50.30301756</v>
       </c>
       <c r="N70">
-        <v>67.52601167999998</v>
+        <v>66.79698243999999</v>
       </c>
       <c r="O70">
-        <v>14.8557225696</v>
+        <v>14.6953361368</v>
       </c>
       <c r="P70">
-        <v>52.67028911039998</v>
+        <v>52.1016463032</v>
       </c>
       <c r="Q70">
-        <v>59.77028911039999</v>
+        <v>59.20164630320001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1594288419084212</v>
+        <v>0.1627908460009381</v>
       </c>
       <c r="T70">
-        <v>1.480964728199582</v>
+        <v>1.524782911976312</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.362125864155204</v>
+        <v>2.327892155979042</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09126072226029082</v>
+        <v>0.09129989510988684</v>
       </c>
       <c r="C71">
-        <v>283.0404174987735</v>
+        <v>273.2077499401846</v>
       </c>
       <c r="D71">
-        <v>688.8686174987735</v>
+        <v>688.6537499401846</v>
       </c>
       <c r="E71">
-        <v>661.9482</v>
+        <v>671.5660000000001</v>
       </c>
       <c r="F71">
-        <v>663.6282</v>
+        <v>673.2460000000001</v>
       </c>
       <c r="G71">
         <v>257.8</v>
@@ -7109,28 +7109,28 @@
         <v>117.1</v>
       </c>
       <c r="M71">
-        <v>50.30301756</v>
+        <v>51.03204680000001</v>
       </c>
       <c r="N71">
-        <v>66.79698243999999</v>
+        <v>66.06795319999998</v>
       </c>
       <c r="O71">
-        <v>14.6953361368</v>
+        <v>14.534949704</v>
       </c>
       <c r="P71">
-        <v>52.1016463032</v>
+        <v>51.53300349599998</v>
       </c>
       <c r="Q71">
-        <v>59.20164630320001</v>
+        <v>58.63300349599999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1627908460009381</v>
+        <v>0.1663769836996228</v>
       </c>
       <c r="T71">
-        <v>1.524782911976312</v>
+        <v>1.571522308004824</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.327892155979042</v>
+        <v>2.294636553750769</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09129989510988684</v>
+        <v>0.09133906795948291</v>
       </c>
       <c r="C72">
-        <v>273.2077499401846</v>
+        <v>263.3752163800696</v>
       </c>
       <c r="D72">
-        <v>688.6537499401846</v>
+        <v>688.4390163800696</v>
       </c>
       <c r="E72">
-        <v>671.5660000000001</v>
+        <v>681.1838000000001</v>
       </c>
       <c r="F72">
-        <v>673.2460000000001</v>
+        <v>682.8638000000001</v>
       </c>
       <c r="G72">
         <v>257.8</v>
@@ -7191,28 +7191,28 @@
         <v>117.1</v>
       </c>
       <c r="M72">
-        <v>51.03204680000001</v>
+        <v>51.76107604000001</v>
       </c>
       <c r="N72">
-        <v>66.06795319999998</v>
+        <v>65.33892395999999</v>
       </c>
       <c r="O72">
-        <v>14.534949704</v>
+        <v>14.3745632712</v>
       </c>
       <c r="P72">
-        <v>51.53300349599998</v>
+        <v>50.96436068879999</v>
       </c>
       <c r="Q72">
-        <v>58.63300349599999</v>
+        <v>58.0643606888</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1663769836996228</v>
+        <v>0.1702104412395962</v>
       </c>
       <c r="T72">
-        <v>1.571522308004824</v>
+        <v>1.621485110655993</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.294636553750769</v>
+        <v>2.262317729050054</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09133906795948291</v>
+        <v>0.09137824080907894</v>
       </c>
       <c r="C73">
-        <v>263.3752163800697</v>
+        <v>253.5428166931189</v>
       </c>
       <c r="D73">
-        <v>688.4390163800696</v>
+        <v>688.2244166931189</v>
       </c>
       <c r="E73">
-        <v>681.1838</v>
+        <v>690.8016</v>
       </c>
       <c r="F73">
-        <v>682.8638</v>
+        <v>692.4816</v>
       </c>
       <c r="G73">
         <v>257.8</v>
@@ -7273,28 +7273,28 @@
         <v>117.1</v>
       </c>
       <c r="M73">
-        <v>51.76107604</v>
+        <v>52.49010528</v>
       </c>
       <c r="N73">
-        <v>65.33892395999999</v>
+        <v>64.60989472</v>
       </c>
       <c r="O73">
-        <v>14.3745632712</v>
+        <v>14.2141768384</v>
       </c>
       <c r="P73">
-        <v>50.96436068879999</v>
+        <v>50.3957178816</v>
       </c>
       <c r="Q73">
-        <v>58.0643606888</v>
+        <v>57.49571788160001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1702104412395962</v>
+        <v>0.1743177171752819</v>
       </c>
       <c r="T73">
-        <v>1.621485110655992</v>
+        <v>1.675016684925101</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.262317729050054</v>
+        <v>2.230896649479915</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09137824080907894</v>
+        <v>0.09141741365867498</v>
       </c>
       <c r="C74">
-        <v>253.5428166931189</v>
+        <v>243.7105507541791</v>
       </c>
       <c r="D74">
-        <v>688.2244166931189</v>
+        <v>688.009950754179</v>
       </c>
       <c r="E74">
-        <v>690.8016</v>
+        <v>700.4194</v>
       </c>
       <c r="F74">
-        <v>692.4816</v>
+        <v>702.0993999999999</v>
       </c>
       <c r="G74">
         <v>257.8</v>
@@ -7355,28 +7355,28 @@
         <v>117.1</v>
       </c>
       <c r="M74">
-        <v>52.49010528</v>
+        <v>53.21913452</v>
       </c>
       <c r="N74">
-        <v>64.60989472</v>
+        <v>63.88086548</v>
       </c>
       <c r="O74">
-        <v>14.2141768384</v>
+        <v>14.0537904056</v>
       </c>
       <c r="P74">
-        <v>50.3957178816</v>
+        <v>49.8270750744</v>
       </c>
       <c r="Q74">
-        <v>57.49571788160001</v>
+        <v>56.92707507440001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1743177171752819</v>
+        <v>0.1787292357728703</v>
       </c>
       <c r="T74">
-        <v>1.675016684925101</v>
+        <v>1.732513560991922</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.230896649479915</v>
+        <v>2.200336421404848</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09141741365867498</v>
+        <v>0.09145658650827101</v>
       </c>
       <c r="C75">
-        <v>243.7105507541791</v>
+        <v>233.8784184382527</v>
       </c>
       <c r="D75">
-        <v>688.009950754179</v>
+        <v>687.7956184382525</v>
       </c>
       <c r="E75">
-        <v>700.4194</v>
+        <v>710.0372</v>
       </c>
       <c r="F75">
-        <v>702.0993999999999</v>
+        <v>711.7171999999999</v>
       </c>
       <c r="G75">
         <v>257.8</v>
@@ -7437,28 +7437,28 @@
         <v>117.1</v>
       </c>
       <c r="M75">
-        <v>53.21913452</v>
+        <v>53.94816376</v>
       </c>
       <c r="N75">
-        <v>63.88086548</v>
+        <v>63.15183623999999</v>
       </c>
       <c r="O75">
-        <v>14.0537904056</v>
+        <v>13.8934039728</v>
       </c>
       <c r="P75">
-        <v>49.8270750744</v>
+        <v>49.25843226719999</v>
       </c>
       <c r="Q75">
-        <v>56.92707507440001</v>
+        <v>56.3584322672</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1787292357728703</v>
+        <v>0.1834801019548885</v>
       </c>
       <c r="T75">
-        <v>1.732513560991922</v>
+        <v>1.794433273679267</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.200336421404848</v>
+        <v>2.170602145439918</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09145658650827101</v>
+        <v>0.09149575935786705</v>
       </c>
       <c r="C76">
-        <v>233.8784184382527</v>
+        <v>224.0464196204973</v>
       </c>
       <c r="D76">
-        <v>687.7956184382525</v>
+        <v>687.5814196204973</v>
       </c>
       <c r="E76">
-        <v>710.0372</v>
+        <v>719.6550000000001</v>
       </c>
       <c r="F76">
-        <v>711.7171999999999</v>
+        <v>721.335</v>
       </c>
       <c r="G76">
         <v>257.8</v>
@@ -7519,28 +7519,28 @@
         <v>117.1</v>
       </c>
       <c r="M76">
-        <v>53.94816376</v>
+        <v>54.67719300000001</v>
       </c>
       <c r="N76">
-        <v>63.15183623999999</v>
+        <v>62.42280699999998</v>
       </c>
       <c r="O76">
-        <v>13.8934039728</v>
+        <v>13.73301754</v>
       </c>
       <c r="P76">
-        <v>49.25843226719999</v>
+        <v>48.68978945999999</v>
       </c>
       <c r="Q76">
-        <v>56.3584322672</v>
+        <v>55.78978945999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1834801019548885</v>
+        <v>0.1886110374314682</v>
       </c>
       <c r="T76">
-        <v>1.794433273679267</v>
+        <v>1.8613065633816</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.170602145439918</v>
+        <v>2.141660783500718</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09149575935786705</v>
+        <v>0.09153493220746309</v>
       </c>
       <c r="C77">
-        <v>224.0464196204973</v>
+        <v>214.214554176227</v>
       </c>
       <c r="D77">
-        <v>687.5814196204973</v>
+        <v>687.3673541762271</v>
       </c>
       <c r="E77">
-        <v>719.6550000000001</v>
+        <v>729.2728000000001</v>
       </c>
       <c r="F77">
-        <v>721.335</v>
+        <v>730.9528</v>
       </c>
       <c r="G77">
         <v>257.8</v>
@@ -7601,28 +7601,28 @@
         <v>117.1</v>
       </c>
       <c r="M77">
-        <v>54.67719300000001</v>
+        <v>55.40622224000001</v>
       </c>
       <c r="N77">
-        <v>62.42280699999998</v>
+        <v>61.69377775999999</v>
       </c>
       <c r="O77">
-        <v>13.73301754</v>
+        <v>13.5726311072</v>
       </c>
       <c r="P77">
-        <v>48.68978945999999</v>
+        <v>48.12114665279999</v>
       </c>
       <c r="Q77">
-        <v>55.78978945999999</v>
+        <v>55.2211466528</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1886110374314682</v>
+        <v>0.1941695508644295</v>
       </c>
       <c r="T77">
-        <v>1.8613065633816</v>
+        <v>1.933752627225794</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.141660783500718</v>
+        <v>2.113481036349393</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09153493220746309</v>
+        <v>0.09157410505705912</v>
       </c>
       <c r="C78">
-        <v>214.214554176227</v>
+        <v>204.3828219809109</v>
       </c>
       <c r="D78">
-        <v>687.3673541762271</v>
+        <v>687.1534219809109</v>
       </c>
       <c r="E78">
-        <v>729.2728000000001</v>
+        <v>738.8906000000001</v>
       </c>
       <c r="F78">
-        <v>730.9528</v>
+        <v>740.5706</v>
       </c>
       <c r="G78">
         <v>257.8</v>
@@ -7683,28 +7683,28 @@
         <v>117.1</v>
       </c>
       <c r="M78">
-        <v>55.40622224000001</v>
+        <v>56.13525148000001</v>
       </c>
       <c r="N78">
-        <v>61.69377775999999</v>
+        <v>60.96474851999999</v>
       </c>
       <c r="O78">
-        <v>13.5726311072</v>
+        <v>13.4122446744</v>
       </c>
       <c r="P78">
-        <v>48.12114665279999</v>
+        <v>47.55250384559999</v>
       </c>
       <c r="Q78">
-        <v>55.2211466528</v>
+        <v>54.65250384559999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1941695508644295</v>
+        <v>0.2002114132915614</v>
       </c>
       <c r="T78">
-        <v>1.933752627225794</v>
+        <v>2.01249834879557</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.113481036349393</v>
+        <v>2.086033230682518</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09157410505705912</v>
+        <v>0.09161327790665516</v>
       </c>
       <c r="C79">
-        <v>204.3828219809109</v>
+        <v>194.5512229101723</v>
       </c>
       <c r="D79">
-        <v>687.1534219809109</v>
+        <v>686.9396229101723</v>
       </c>
       <c r="E79">
-        <v>738.8906000000001</v>
+        <v>748.5084000000001</v>
       </c>
       <c r="F79">
-        <v>740.5706</v>
+        <v>750.1884</v>
       </c>
       <c r="G79">
         <v>257.8</v>
@@ -7765,28 +7765,28 @@
         <v>117.1</v>
       </c>
       <c r="M79">
-        <v>56.13525148000001</v>
+        <v>56.86428072</v>
       </c>
       <c r="N79">
-        <v>60.96474851999999</v>
+        <v>60.23571927999999</v>
       </c>
       <c r="O79">
-        <v>13.4122446744</v>
+        <v>13.2518582416</v>
       </c>
       <c r="P79">
-        <v>47.55250384559999</v>
+        <v>46.98386103839999</v>
       </c>
       <c r="Q79">
-        <v>54.65250384559999</v>
+        <v>54.0838610384</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2002114132915614</v>
+        <v>0.2068025359393417</v>
       </c>
       <c r="T79">
-        <v>2.01249834879557</v>
+        <v>2.098402772326235</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.086033230682518</v>
+        <v>2.059289214904537</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09161327790665516</v>
+        <v>0.09165245075625121</v>
       </c>
       <c r="C80">
-        <v>194.5512229101723</v>
+        <v>184.7197568397899</v>
       </c>
       <c r="D80">
-        <v>686.9396229101723</v>
+        <v>686.7259568397899</v>
       </c>
       <c r="E80">
-        <v>748.5084000000001</v>
+        <v>758.1262</v>
       </c>
       <c r="F80">
-        <v>750.1884</v>
+        <v>759.8062</v>
       </c>
       <c r="G80">
         <v>257.8</v>
@@ -7847,28 +7847,28 @@
         <v>117.1</v>
       </c>
       <c r="M80">
-        <v>56.86428072</v>
+        <v>57.59330996000001</v>
       </c>
       <c r="N80">
-        <v>60.23571927999999</v>
+        <v>59.50669003999999</v>
       </c>
       <c r="O80">
-        <v>13.2518582416</v>
+        <v>13.0914718088</v>
       </c>
       <c r="P80">
-        <v>46.98386103839999</v>
+        <v>46.41521823119999</v>
       </c>
       <c r="Q80">
-        <v>54.0838610384</v>
+        <v>53.5152182312</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2068025359393417</v>
+        <v>0.2140213845535772</v>
       </c>
       <c r="T80">
-        <v>2.098402772326235</v>
+        <v>2.192488569526487</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.059289214904537</v>
+        <v>2.033222262817137</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09165245075625121</v>
+        <v>0.09169162360584726</v>
       </c>
       <c r="C81">
-        <v>184.7197568397899</v>
+        <v>174.888423645697</v>
       </c>
       <c r="D81">
-        <v>686.7259568397899</v>
+        <v>686.5124236456969</v>
       </c>
       <c r="E81">
-        <v>758.1262</v>
+        <v>767.744</v>
       </c>
       <c r="F81">
-        <v>759.8062</v>
+        <v>769.424</v>
       </c>
       <c r="G81">
         <v>257.8</v>
@@ -7929,28 +7929,28 @@
         <v>117.1</v>
       </c>
       <c r="M81">
-        <v>57.59330996000001</v>
+        <v>58.3223392</v>
       </c>
       <c r="N81">
-        <v>59.50669003999999</v>
+        <v>58.77766079999999</v>
       </c>
       <c r="O81">
-        <v>13.0914718088</v>
+        <v>12.931085376</v>
       </c>
       <c r="P81">
-        <v>46.41521823119999</v>
+        <v>45.84657542399999</v>
       </c>
       <c r="Q81">
-        <v>53.5152182312</v>
+        <v>52.946575424</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2140213845535772</v>
+        <v>0.2219621180292362</v>
       </c>
       <c r="T81">
-        <v>2.192488569526487</v>
+        <v>2.295982946446764</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.033222262817137</v>
+        <v>2.007806984531924</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09169162360584726</v>
+        <v>0.1007023564554433</v>
       </c>
       <c r="C82">
-        <v>174.888423645697</v>
+        <v>119.4455638176149</v>
       </c>
       <c r="D82">
-        <v>686.5124236456969</v>
+        <v>640.6873638176149</v>
       </c>
       <c r="E82">
-        <v>767.744</v>
+        <v>777.3618000000001</v>
       </c>
       <c r="F82">
-        <v>769.424</v>
+        <v>779.0418000000001</v>
       </c>
       <c r="G82">
         <v>257.8</v>
@@ -8011,45 +8011,45 @@
         <v>117.1</v>
       </c>
       <c r="M82">
-        <v>58.3223392</v>
+        <v>70.11376200000001</v>
       </c>
       <c r="N82">
-        <v>58.77766079999999</v>
+        <v>46.98623799999999</v>
       </c>
       <c r="O82">
-        <v>12.931085376</v>
+        <v>10.33697236</v>
       </c>
       <c r="P82">
-        <v>45.84657542399999</v>
+        <v>36.64926563999999</v>
       </c>
       <c r="Q82">
-        <v>52.946575424</v>
+        <v>43.74926564</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2219621180292362</v>
+        <v>0.2307387181865436</v>
       </c>
       <c r="T82">
-        <v>2.295982946446764</v>
+        <v>2.410371468306018</v>
       </c>
       <c r="U82">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V82">
         <v>0.22</v>
       </c>
       <c r="W82">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.007806984531924</v>
+        <v>1.670142874376074</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1007023564554433</v>
+        <v>0.1008522893050393</v>
       </c>
       <c r="C83">
-        <v>119.4455638176149</v>
+        <v>109.1169507842579</v>
       </c>
       <c r="D83">
-        <v>640.6873638176149</v>
+        <v>639.9765507842581</v>
       </c>
       <c r="E83">
-        <v>777.3618000000001</v>
+        <v>786.9796000000001</v>
       </c>
       <c r="F83">
-        <v>779.0418000000001</v>
+        <v>788.6596000000001</v>
       </c>
       <c r="G83">
         <v>257.8</v>
@@ -8093,28 +8093,28 @@
         <v>117.1</v>
       </c>
       <c r="M83">
-        <v>70.11376200000001</v>
+        <v>70.979364</v>
       </c>
       <c r="N83">
-        <v>46.98623799999999</v>
+        <v>46.12063599999999</v>
       </c>
       <c r="O83">
-        <v>10.33697236</v>
+        <v>10.14653992</v>
       </c>
       <c r="P83">
-        <v>36.64926563999999</v>
+        <v>35.97409608</v>
       </c>
       <c r="Q83">
-        <v>43.74926564</v>
+        <v>43.07409608</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2307387181865436</v>
+        <v>0.2404904961391074</v>
       </c>
       <c r="T83">
-        <v>2.410371468306018</v>
+        <v>2.537469825927412</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.670142874376074</v>
+        <v>1.649775278347098</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1008522893050393</v>
+        <v>0.1010022221546353</v>
       </c>
       <c r="C84">
-        <v>109.1169507842579</v>
+        <v>98.78991323142679</v>
       </c>
       <c r="D84">
-        <v>639.9765507842581</v>
+        <v>639.2673132314268</v>
       </c>
       <c r="E84">
-        <v>786.9796000000001</v>
+        <v>796.5974000000001</v>
       </c>
       <c r="F84">
-        <v>788.6596000000001</v>
+        <v>798.2774000000001</v>
       </c>
       <c r="G84">
         <v>257.8</v>
@@ -8175,28 +8175,28 @@
         <v>117.1</v>
       </c>
       <c r="M84">
-        <v>70.979364</v>
+        <v>71.844966</v>
       </c>
       <c r="N84">
-        <v>46.12063599999999</v>
+        <v>45.25503399999999</v>
       </c>
       <c r="O84">
-        <v>10.14653992</v>
+        <v>9.956107479999998</v>
       </c>
       <c r="P84">
-        <v>35.97409608</v>
+        <v>35.29892651999999</v>
       </c>
       <c r="Q84">
-        <v>43.07409608</v>
+        <v>42.39892652</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2404904961391074</v>
+        <v>0.2513895420860904</v>
       </c>
       <c r="T84">
-        <v>2.537469825927412</v>
+        <v>2.679520931504263</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.649775278347098</v>
+        <v>1.629898467764603</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1010022221546353</v>
+        <v>0.1011521550042314</v>
       </c>
       <c r="C85">
-        <v>98.78991323142679</v>
+        <v>88.46444592696218</v>
       </c>
       <c r="D85">
-        <v>639.2673132314268</v>
+        <v>638.5596459269622</v>
       </c>
       <c r="E85">
-        <v>796.5974000000001</v>
+        <v>806.2152000000001</v>
       </c>
       <c r="F85">
-        <v>798.2774000000001</v>
+        <v>807.8952</v>
       </c>
       <c r="G85">
         <v>257.8</v>
@@ -8257,28 +8257,28 @@
         <v>117.1</v>
       </c>
       <c r="M85">
-        <v>71.844966</v>
+        <v>72.71056799999999</v>
       </c>
       <c r="N85">
-        <v>45.25503399999999</v>
+        <v>44.389432</v>
       </c>
       <c r="O85">
-        <v>9.956107479999998</v>
+        <v>9.76567504</v>
       </c>
       <c r="P85">
-        <v>35.29892651999999</v>
+        <v>34.62375696</v>
       </c>
       <c r="Q85">
-        <v>42.39892652</v>
+        <v>41.72375696000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2513895420860904</v>
+        <v>0.2636509687764463</v>
       </c>
       <c r="T85">
-        <v>2.679520931504263</v>
+        <v>2.839328425278221</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.629898467764603</v>
+        <v>1.610494914576929</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1011521550042314</v>
+        <v>0.1013020878538274</v>
       </c>
       <c r="C86">
-        <v>88.4644459269623</v>
+        <v>78.14054366184791</v>
       </c>
       <c r="D86">
-        <v>638.5596459269622</v>
+        <v>637.8535436618478</v>
       </c>
       <c r="E86">
-        <v>806.2152</v>
+        <v>815.833</v>
       </c>
       <c r="F86">
-        <v>807.8951999999999</v>
+        <v>817.5129999999999</v>
       </c>
       <c r="G86">
         <v>257.8</v>
@@ -8339,28 +8339,28 @@
         <v>117.1</v>
       </c>
       <c r="M86">
-        <v>72.71056799999999</v>
+        <v>73.57616999999999</v>
       </c>
       <c r="N86">
-        <v>44.389432</v>
+        <v>43.52383</v>
       </c>
       <c r="O86">
-        <v>9.76567504</v>
+        <v>9.575242600000001</v>
       </c>
       <c r="P86">
-        <v>34.62375696</v>
+        <v>33.9485874</v>
       </c>
       <c r="Q86">
-        <v>41.72375696000001</v>
+        <v>41.04858740000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2636509687764462</v>
+        <v>0.2775472523588495</v>
       </c>
       <c r="T86">
-        <v>2.839328425278219</v>
+        <v>3.020443584888704</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.610494914576929</v>
+        <v>1.591547915581907</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1013020878538274</v>
+        <v>0.1014520207034235</v>
       </c>
       <c r="C87">
-        <v>78.14054366184791</v>
+        <v>67.81820125008153</v>
       </c>
       <c r="D87">
-        <v>637.8535436618478</v>
+        <v>637.1490012500814</v>
       </c>
       <c r="E87">
-        <v>815.833</v>
+        <v>825.4508</v>
       </c>
       <c r="F87">
-        <v>817.5129999999999</v>
+        <v>827.1307999999999</v>
       </c>
       <c r="G87">
         <v>257.8</v>
@@ -8421,28 +8421,28 @@
         <v>117.1</v>
       </c>
       <c r="M87">
-        <v>73.57616999999999</v>
+        <v>74.44177199999999</v>
       </c>
       <c r="N87">
-        <v>43.52383</v>
+        <v>42.65822800000001</v>
       </c>
       <c r="O87">
-        <v>9.575242600000001</v>
+        <v>9.384810160000002</v>
       </c>
       <c r="P87">
-        <v>33.9485874</v>
+        <v>33.27341784000001</v>
       </c>
       <c r="Q87">
-        <v>41.04858740000001</v>
+        <v>40.37341784000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2775472523588495</v>
+        <v>0.2934287193101676</v>
       </c>
       <c r="T87">
-        <v>3.020443584888704</v>
+        <v>3.227432338729258</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.591547915581907</v>
+        <v>1.573041544470489</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1014520207034235</v>
+        <v>0.1016019535530195</v>
       </c>
       <c r="C88">
-        <v>67.81820125008153</v>
+        <v>57.49741352854846</v>
       </c>
       <c r="D88">
-        <v>637.1490012500814</v>
+        <v>636.4460135285484</v>
       </c>
       <c r="E88">
-        <v>825.4508</v>
+        <v>835.0686000000001</v>
       </c>
       <c r="F88">
-        <v>827.1307999999999</v>
+        <v>836.7486</v>
       </c>
       <c r="G88">
         <v>257.8</v>
@@ -8503,28 +8503,28 @@
         <v>117.1</v>
       </c>
       <c r="M88">
-        <v>74.44177199999999</v>
+        <v>75.307374</v>
       </c>
       <c r="N88">
-        <v>42.65822800000001</v>
+        <v>41.792626</v>
       </c>
       <c r="O88">
-        <v>9.384810160000002</v>
+        <v>9.19437772</v>
       </c>
       <c r="P88">
-        <v>33.27341784000001</v>
+        <v>32.59824828</v>
       </c>
       <c r="Q88">
-        <v>40.37341784000002</v>
+        <v>39.69824828000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2934287193101676</v>
+        <v>0.3117534888693809</v>
       </c>
       <c r="T88">
-        <v>3.227432338729258</v>
+        <v>3.46626551623759</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.573041544470489</v>
+        <v>1.554960607177725</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1016019535530195</v>
+        <v>0.1017518864026156</v>
       </c>
       <c r="C89">
-        <v>57.49741352854846</v>
+        <v>47.17817535689585</v>
       </c>
       <c r="D89">
-        <v>636.4460135285484</v>
+        <v>635.7445753568959</v>
       </c>
       <c r="E89">
-        <v>835.0686000000001</v>
+        <v>844.6864</v>
       </c>
       <c r="F89">
-        <v>836.7486</v>
+        <v>846.3664</v>
       </c>
       <c r="G89">
         <v>257.8</v>
@@ -8585,28 +8585,28 @@
         <v>117.1</v>
       </c>
       <c r="M89">
-        <v>75.307374</v>
+        <v>76.17297599999999</v>
       </c>
       <c r="N89">
-        <v>41.792626</v>
+        <v>40.927024</v>
       </c>
       <c r="O89">
-        <v>9.19437772</v>
+        <v>9.00394528</v>
       </c>
       <c r="P89">
-        <v>32.59824828</v>
+        <v>31.92307872</v>
       </c>
       <c r="Q89">
-        <v>39.69824828000001</v>
+        <v>39.02307872000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3117534888693809</v>
+        <v>0.333132386688463</v>
       </c>
       <c r="T89">
-        <v>3.46626551623759</v>
+        <v>3.744904223330645</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.554960607177725</v>
+        <v>1.537290600277978</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1017518864026156</v>
+        <v>0.1019018192522116</v>
       </c>
       <c r="C90">
-        <v>47.17817535689585</v>
+        <v>36.86048161740689</v>
       </c>
       <c r="D90">
-        <v>635.7445753568959</v>
+        <v>635.0446816174069</v>
       </c>
       <c r="E90">
-        <v>844.6864</v>
+        <v>854.3042</v>
       </c>
       <c r="F90">
-        <v>846.3664</v>
+        <v>855.9842</v>
       </c>
       <c r="G90">
         <v>257.8</v>
@@ -8667,28 +8667,28 @@
         <v>117.1</v>
       </c>
       <c r="M90">
-        <v>76.17297599999999</v>
+        <v>77.038578</v>
       </c>
       <c r="N90">
-        <v>40.927024</v>
+        <v>40.06142199999999</v>
       </c>
       <c r="O90">
-        <v>9.00394528</v>
+        <v>8.813512839999998</v>
       </c>
       <c r="P90">
-        <v>31.92307872</v>
+        <v>31.24790916</v>
       </c>
       <c r="Q90">
-        <v>39.02307872000002</v>
+        <v>38.34790916</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.333132386688463</v>
+        <v>0.3583983568382872</v>
       </c>
       <c r="T90">
-        <v>3.744904223330645</v>
+        <v>4.074204513531527</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.537290600277978</v>
+        <v>1.520017672184967</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1019018192522116</v>
+        <v>0.1020517521018076</v>
       </c>
       <c r="C91">
-        <v>36.86048161740689</v>
+        <v>26.54432721487626</v>
       </c>
       <c r="D91">
-        <v>635.0446816174069</v>
+        <v>634.3463272148762</v>
       </c>
       <c r="E91">
-        <v>854.3042</v>
+        <v>863.922</v>
       </c>
       <c r="F91">
-        <v>855.9842</v>
+        <v>865.602</v>
       </c>
       <c r="G91">
         <v>257.8</v>
@@ -8749,28 +8749,28 @@
         <v>117.1</v>
       </c>
       <c r="M91">
-        <v>77.038578</v>
+        <v>77.90418</v>
       </c>
       <c r="N91">
-        <v>40.06142199999999</v>
+        <v>39.19582</v>
       </c>
       <c r="O91">
-        <v>8.813512839999998</v>
+        <v>8.623080399999999</v>
       </c>
       <c r="P91">
-        <v>31.24790916</v>
+        <v>30.5727396</v>
       </c>
       <c r="Q91">
-        <v>38.34790916</v>
+        <v>37.67273960000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3583983568382872</v>
+        <v>0.3887175210180764</v>
       </c>
       <c r="T91">
-        <v>4.074204513531527</v>
+        <v>4.469364861772585</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.520017672184967</v>
+        <v>1.503128586938467</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1020517521018076</v>
+        <v>0.1458802752461776</v>
       </c>
       <c r="C92">
-        <v>26.54432721487626</v>
+        <v>-137.3866097541783</v>
       </c>
       <c r="D92">
-        <v>634.3463272148762</v>
+        <v>480.0331902458217</v>
       </c>
       <c r="E92">
-        <v>863.922</v>
+        <v>873.5398</v>
       </c>
       <c r="F92">
-        <v>865.602</v>
+        <v>875.2198</v>
       </c>
       <c r="G92">
         <v>257.8</v>
@@ -8831,45 +8831,45 @@
         <v>117.1</v>
       </c>
       <c r="M92">
-        <v>77.90418</v>
+        <v>128.48226664</v>
       </c>
       <c r="N92">
-        <v>39.19582</v>
+        <v>-11.38226664000001</v>
       </c>
       <c r="O92">
-        <v>8.623080399999999</v>
+        <v>-2.504098660800003</v>
       </c>
       <c r="P92">
-        <v>30.5727396</v>
+        <v>-8.878167979200009</v>
       </c>
       <c r="Q92">
-        <v>37.67273960000001</v>
+        <v>-1.778167979200001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3887175210180764</v>
+        <v>0.4342002962824567</v>
       </c>
       <c r="T92">
-        <v>4.469364861772585</v>
+        <v>5.062157895441475</v>
       </c>
       <c r="U92">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.22</v>
+        <v>0.2005101612363647</v>
       </c>
       <c r="W92">
-        <v>0.0702</v>
+        <v>0.1173651083305017</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>1.503128586938467</v>
+        <v>0.9114098238016576</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1458802752461776</v>
+        <v>0.1468902752461776</v>
       </c>
       <c r="C93">
-        <v>-137.3866097541783</v>
+        <v>-149.68039974622</v>
       </c>
       <c r="D93">
-        <v>480.0331902458217</v>
+        <v>477.35720025378</v>
       </c>
       <c r="E93">
-        <v>873.5398</v>
+        <v>883.1576000000001</v>
       </c>
       <c r="F93">
-        <v>875.2198</v>
+        <v>884.8376000000001</v>
       </c>
       <c r="G93">
         <v>257.8</v>
@@ -8913,37 +8913,37 @@
         <v>117.1</v>
       </c>
       <c r="M93">
-        <v>128.48226664</v>
+        <v>129.89415968</v>
       </c>
       <c r="N93">
-        <v>-11.38226664000001</v>
+        <v>-12.79415968000004</v>
       </c>
       <c r="O93">
-        <v>-2.504098660800003</v>
+        <v>-2.814715129600008</v>
       </c>
       <c r="P93">
-        <v>-8.878167979200009</v>
+        <v>-9.979444550400029</v>
       </c>
       <c r="Q93">
-        <v>-1.778167979200001</v>
+        <v>-2.87944455040002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4342002962824567</v>
+        <v>0.4827503333177639</v>
       </c>
       <c r="T93">
-        <v>5.062157895441475</v>
+        <v>5.694927632371661</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2005101612363647</v>
+        <v>0.1983307029620563</v>
       </c>
       <c r="W93">
-        <v>0.1173651083305017</v>
+        <v>0.1176850528051701</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.9114098238016576</v>
+        <v>0.9015031952820742</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1468902752461776</v>
+        <v>0.1479002752461776</v>
       </c>
       <c r="C94">
-        <v>-149.68039974622</v>
+        <v>-161.9445200210462</v>
       </c>
       <c r="D94">
-        <v>477.35720025378</v>
+        <v>474.7108799789539</v>
       </c>
       <c r="E94">
-        <v>883.1576000000001</v>
+        <v>892.7754000000001</v>
       </c>
       <c r="F94">
-        <v>884.8376000000001</v>
+        <v>894.4554000000001</v>
       </c>
       <c r="G94">
         <v>257.8</v>
@@ -8995,37 +8995,37 @@
         <v>117.1</v>
       </c>
       <c r="M94">
-        <v>129.89415968</v>
+        <v>131.30605272</v>
       </c>
       <c r="N94">
-        <v>-12.79415968000004</v>
+        <v>-14.20605272000003</v>
       </c>
       <c r="O94">
-        <v>-2.814715129600008</v>
+        <v>-3.125331598400007</v>
       </c>
       <c r="P94">
-        <v>-9.979444550400029</v>
+        <v>-11.08072112160002</v>
       </c>
       <c r="Q94">
-        <v>-2.87944455040002</v>
+        <v>-3.980721121600016</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4827503333177639</v>
+        <v>0.5451718095060158</v>
       </c>
       <c r="T94">
-        <v>5.694927632371661</v>
+        <v>6.50848872271047</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1983307029620563</v>
+        <v>0.1961981147581633</v>
       </c>
       <c r="W94">
-        <v>0.1176850528051701</v>
+        <v>0.1179981167535016</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.9015031952820742</v>
+        <v>0.8918096125371057</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1479002752461776</v>
+        <v>0.1489102752461776</v>
       </c>
       <c r="C95">
-        <v>-161.9445200210462</v>
+        <v>-174.1794612973964</v>
       </c>
       <c r="D95">
-        <v>474.7108799789539</v>
+        <v>472.0937387026036</v>
       </c>
       <c r="E95">
-        <v>892.7754000000001</v>
+        <v>902.3932000000001</v>
       </c>
       <c r="F95">
-        <v>894.4554000000001</v>
+        <v>904.0732</v>
       </c>
       <c r="G95">
         <v>257.8</v>
@@ -9077,37 +9077,37 @@
         <v>117.1</v>
       </c>
       <c r="M95">
-        <v>131.30605272</v>
+        <v>132.71794576</v>
       </c>
       <c r="N95">
-        <v>-14.20605272000003</v>
+        <v>-15.61794576000003</v>
       </c>
       <c r="O95">
-        <v>-3.125331598400007</v>
+        <v>-3.435948067200006</v>
       </c>
       <c r="P95">
-        <v>-11.08072112160002</v>
+        <v>-12.18199769280002</v>
       </c>
       <c r="Q95">
-        <v>-3.980721121600016</v>
+        <v>-5.081997692800012</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5451718095060158</v>
+        <v>0.6284004444236853</v>
       </c>
       <c r="T95">
-        <v>6.50848872271047</v>
+        <v>7.593236843162217</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1961981147581633</v>
+        <v>0.1941109007713743</v>
       </c>
       <c r="W95">
-        <v>0.1179981167535016</v>
+        <v>0.1183045197667623</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8918096125371057</v>
+        <v>0.8823222762335194</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1489102752461776</v>
+        <v>0.1499202752461776</v>
       </c>
       <c r="C96">
-        <v>-174.1794612973964</v>
+        <v>-186.3857035317658</v>
       </c>
       <c r="D96">
-        <v>472.0937387026036</v>
+        <v>469.5052964682343</v>
       </c>
       <c r="E96">
-        <v>902.3932000000001</v>
+        <v>912.0110000000001</v>
       </c>
       <c r="F96">
-        <v>904.0732</v>
+        <v>913.691</v>
       </c>
       <c r="G96">
         <v>257.8</v>
@@ -9159,37 +9159,37 @@
         <v>117.1</v>
       </c>
       <c r="M96">
-        <v>132.71794576</v>
+        <v>134.1298388</v>
       </c>
       <c r="N96">
-        <v>-15.61794576000003</v>
+        <v>-17.02983880000002</v>
       </c>
       <c r="O96">
-        <v>-3.435948067200006</v>
+        <v>-3.746564536000005</v>
       </c>
       <c r="P96">
-        <v>-12.18199769280002</v>
+        <v>-13.28327426400002</v>
       </c>
       <c r="Q96">
-        <v>-5.081997692800012</v>
+        <v>-6.183274264000008</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6284004444236853</v>
+        <v>0.7449205333084228</v>
       </c>
       <c r="T96">
-        <v>7.593236843162217</v>
+        <v>9.111884211794665</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1941109007713743</v>
+        <v>0.1920676281316756</v>
       </c>
       <c r="W96">
-        <v>0.1183045197667623</v>
+        <v>0.11860447219027</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8823222762335194</v>
+        <v>0.8730346733257983</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1499202752461776</v>
+        <v>0.1509302752461776</v>
       </c>
       <c r="C97">
-        <v>-186.3857035317658</v>
+        <v>-198.5637162118364</v>
       </c>
       <c r="D97">
-        <v>469.5052964682343</v>
+        <v>466.9450837881636</v>
       </c>
       <c r="E97">
-        <v>912.0110000000001</v>
+        <v>921.6288000000001</v>
       </c>
       <c r="F97">
-        <v>913.691</v>
+        <v>923.3088</v>
       </c>
       <c r="G97">
         <v>257.8</v>
@@ -9241,37 +9241,37 @@
         <v>117.1</v>
       </c>
       <c r="M97">
-        <v>134.1298388</v>
+        <v>135.54173184</v>
       </c>
       <c r="N97">
-        <v>-17.02983880000002</v>
+        <v>-18.44173184000002</v>
       </c>
       <c r="O97">
-        <v>-3.746564536000005</v>
+        <v>-4.057181004800004</v>
       </c>
       <c r="P97">
-        <v>-13.28327426400002</v>
+        <v>-14.38455083520001</v>
       </c>
       <c r="Q97">
-        <v>-6.183274264000008</v>
+        <v>-7.284550835200005</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7449205333084228</v>
+        <v>0.9197006666355287</v>
       </c>
       <c r="T97">
-        <v>9.111884211794665</v>
+        <v>11.38985526474334</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1920676281316756</v>
+        <v>0.1900669236719707</v>
       </c>
       <c r="W97">
-        <v>0.11860447219027</v>
+        <v>0.1188981756049547</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8730346733257983</v>
+        <v>0.8639405621453212</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1509302752461776</v>
+        <v>0.1519402752461776</v>
       </c>
       <c r="C98">
-        <v>-198.5637162118361</v>
+        <v>-210.7139586403626</v>
       </c>
       <c r="D98">
-        <v>466.9450837881638</v>
+        <v>464.4126413596372</v>
       </c>
       <c r="E98">
-        <v>921.6288</v>
+        <v>931.2465999999999</v>
       </c>
       <c r="F98">
-        <v>923.3087999999999</v>
+        <v>932.9265999999999</v>
       </c>
       <c r="G98">
         <v>257.8</v>
@@ -9323,37 +9323,37 @@
         <v>117.1</v>
       </c>
       <c r="M98">
-        <v>135.54173184</v>
+        <v>136.95362488</v>
       </c>
       <c r="N98">
-        <v>-18.44173184000002</v>
+        <v>-19.85362488000001</v>
       </c>
       <c r="O98">
-        <v>-4.057181004800004</v>
+        <v>-4.367797473600003</v>
       </c>
       <c r="P98">
-        <v>-14.38455083520001</v>
+        <v>-15.48582740640001</v>
       </c>
       <c r="Q98">
-        <v>-7.284550835200005</v>
+        <v>-8.385827406400001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9197006666355264</v>
+        <v>1.211000888847369</v>
       </c>
       <c r="T98">
-        <v>11.38985526474331</v>
+        <v>15.18647368632441</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1900669236719707</v>
+        <v>0.1881074708506102</v>
       </c>
       <c r="W98">
-        <v>0.1188981756049547</v>
+        <v>0.1191858232791304</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8639405621453212</v>
+        <v>0.8550339584118644</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1519402752461776</v>
+        <v>0.1529502752461776</v>
       </c>
       <c r="C99">
-        <v>-210.7139586403626</v>
+        <v>-222.8368802098676</v>
       </c>
       <c r="D99">
-        <v>464.4126413596372</v>
+        <v>461.9075197901325</v>
       </c>
       <c r="E99">
-        <v>931.2465999999999</v>
+        <v>940.8644</v>
       </c>
       <c r="F99">
-        <v>932.9265999999999</v>
+        <v>942.5444</v>
       </c>
       <c r="G99">
         <v>257.8</v>
@@ -9405,37 +9405,37 @@
         <v>117.1</v>
       </c>
       <c r="M99">
-        <v>136.95362488</v>
+        <v>138.36551792</v>
       </c>
       <c r="N99">
-        <v>-19.85362488000001</v>
+        <v>-21.26551792000001</v>
       </c>
       <c r="O99">
-        <v>-4.367797473600003</v>
+        <v>-4.678413942400002</v>
       </c>
       <c r="P99">
-        <v>-15.48582740640001</v>
+        <v>-16.58710397760001</v>
       </c>
       <c r="Q99">
-        <v>-8.385827406400001</v>
+        <v>-9.487103977599997</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.211000888847369</v>
+        <v>1.793601333271053</v>
       </c>
       <c r="T99">
-        <v>15.18647368632441</v>
+        <v>22.77971052948661</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1881074708506102</v>
+        <v>0.1861880068623386</v>
       </c>
       <c r="W99">
-        <v>0.1191858232791304</v>
+        <v>0.1194676005926087</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8550339584118644</v>
+        <v>0.8463091221015392</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1529502752461776</v>
+        <v>0.1539602752461776</v>
       </c>
       <c r="C100">
-        <v>-222.8368802098676</v>
+        <v>-234.9329206684946</v>
       </c>
       <c r="D100">
-        <v>461.9075197901325</v>
+        <v>459.4292793315054</v>
       </c>
       <c r="E100">
-        <v>940.8644</v>
+        <v>950.4822</v>
       </c>
       <c r="F100">
-        <v>942.5444</v>
+        <v>952.1622</v>
       </c>
       <c r="G100">
         <v>257.8</v>
@@ -9487,37 +9487,37 @@
         <v>117.1</v>
       </c>
       <c r="M100">
-        <v>138.36551792</v>
+        <v>139.77741096</v>
       </c>
       <c r="N100">
-        <v>-21.26551792000001</v>
+        <v>-22.67741096</v>
       </c>
       <c r="O100">
-        <v>-4.678413942400002</v>
+        <v>-4.989030411200001</v>
       </c>
       <c r="P100">
-        <v>-16.58710397760001</v>
+        <v>-17.6883805488</v>
       </c>
       <c r="Q100">
-        <v>-9.487103977599997</v>
+        <v>-10.58838054879999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.793601333271053</v>
+        <v>3.541402666542105</v>
       </c>
       <c r="T100">
-        <v>22.77971052948661</v>
+        <v>45.55942105897321</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1861880068623386</v>
+        <v>0.1843073199243352</v>
       </c>
       <c r="W100">
-        <v>0.1194676005926087</v>
+        <v>0.1197436854351076</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8463091221015392</v>
+        <v>0.8377605451106146</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1539602752461776</v>
-      </c>
-      <c r="C101">
-        <v>-234.9329206684946</v>
-      </c>
-      <c r="D101">
-        <v>459.4292793315054</v>
-      </c>
-      <c r="E101">
-        <v>950.4822</v>
-      </c>
-      <c r="F101">
-        <v>952.1622</v>
-      </c>
-      <c r="G101">
-        <v>257.8</v>
-      </c>
-      <c r="H101">
-        <v>960.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>124.2</v>
-      </c>
-      <c r="K101">
-        <v>7.100000000000009</v>
-      </c>
-      <c r="L101">
-        <v>117.1</v>
-      </c>
-      <c r="M101">
-        <v>139.77741096</v>
-      </c>
-      <c r="N101">
-        <v>-22.67741096</v>
-      </c>
-      <c r="O101">
-        <v>-4.989030411200001</v>
-      </c>
-      <c r="P101">
-        <v>-17.6883805488</v>
-      </c>
-      <c r="Q101">
-        <v>-10.58838054879999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.541402666542105</v>
-      </c>
-      <c r="T101">
-        <v>45.55942105897321</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1843073199243352</v>
-      </c>
-      <c r="W101">
-        <v>0.1197436854351076</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8377605451106146</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
